--- a/IPEDS_Duplicates_list.xlsx
+++ b/IPEDS_Duplicates_list.xlsx
@@ -14,99 +14,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
-    <t>UNITID</t>
+    <t>unitid</t>
   </si>
   <si>
-    <t>CIPCODE</t>
+    <t>cipcode</t>
   </si>
   <si>
-    <t>CTOTALT</t>
+    <t>ctotalt</t>
   </si>
   <si>
-    <t>AWLEVEL</t>
+    <t>awlevel</t>
   </si>
   <si>
-    <t>CTOTALM</t>
+    <t>ctotalm</t>
   </si>
   <si>
-    <t>CTOTALW</t>
+    <t>ctotalw</t>
   </si>
   <si>
-    <t>CUNKNT</t>
+    <t>cunknt</t>
   </si>
   <si>
-    <t>CBKAAT</t>
+    <t>cbkaat</t>
   </si>
   <si>
-    <t>CASIAT</t>
+    <t>casiat</t>
   </si>
   <si>
-    <t>CNHPIT</t>
+    <t>cnhpit</t>
   </si>
   <si>
-    <t>CHISPT</t>
+    <t>chispt</t>
   </si>
   <si>
-    <t>CWHITT</t>
+    <t>cwhitt</t>
   </si>
   <si>
-    <t>C2MORT</t>
+    <t>c2mort</t>
   </si>
   <si>
-    <t>CNRALT</t>
+    <t>cnralt</t>
   </si>
   <si>
-    <t>CBKAAM</t>
+    <t>cbkaam</t>
   </si>
   <si>
-    <t>CASIAM</t>
+    <t>casiam</t>
   </si>
   <si>
-    <t>CNHPIM</t>
+    <t>cnhpim</t>
   </si>
   <si>
-    <t>CHISPM</t>
+    <t>chispm</t>
   </si>
   <si>
-    <t>CWHITM</t>
+    <t>cwhitm</t>
   </si>
   <si>
-    <t>CUNKNM</t>
+    <t>cunknm</t>
   </si>
   <si>
-    <t>C2MORM</t>
+    <t>c2morm</t>
   </si>
   <si>
-    <t>CNRALM</t>
+    <t>cnralm</t>
   </si>
   <si>
-    <t>CBKAAW</t>
+    <t>cbkaaw</t>
   </si>
   <si>
-    <t>CASIAW</t>
+    <t>casiaw</t>
   </si>
   <si>
-    <t>CNHPIW</t>
+    <t>cnhpiw</t>
   </si>
   <si>
-    <t>CHISPW</t>
+    <t>chispw</t>
   </si>
   <si>
-    <t>CWHITW</t>
+    <t>cwhitw</t>
   </si>
   <si>
-    <t>CUNKNW</t>
+    <t>cunknw</t>
   </si>
   <si>
-    <t>C2MORW</t>
+    <t>c2morw</t>
   </si>
   <si>
-    <t>CNRALW</t>
+    <t>cnralw</t>
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>MAJORNUM_STD</t>
   </si>
   <si>
     <t>CRACE17_STD</t>
@@ -482,10 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK373"/>
+  <dimension ref="A1:AL373"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,8 +600,11 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:37">
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38">
       <c r="A2">
         <v>110422</v>
       </c>
@@ -621,7 +627,7 @@
         <v>2006</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -636,10 +642,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38">
       <c r="A3">
         <v>110422</v>
       </c>
@@ -662,7 +671,7 @@
         <v>2006</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -679,8 +688,11 @@
       <c r="AK3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:37">
+      <c r="AL3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38">
       <c r="A4">
         <v>110422</v>
       </c>
@@ -774,8 +786,11 @@
       <c r="AE4">
         <v>2012</v>
       </c>
-    </row>
-    <row r="5" spans="1:37">
+      <c r="AF4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38">
       <c r="A5">
         <v>110422</v>
       </c>
@@ -869,8 +884,11 @@
       <c r="AE5">
         <v>2012</v>
       </c>
-    </row>
-    <row r="6" spans="1:37">
+      <c r="AF5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38">
       <c r="A6">
         <v>110422</v>
       </c>
@@ -964,8 +982,11 @@
       <c r="AE6">
         <v>2013</v>
       </c>
-    </row>
-    <row r="7" spans="1:37">
+      <c r="AF6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
       <c r="A7">
         <v>110422</v>
       </c>
@@ -1059,8 +1080,11 @@
       <c r="AE7">
         <v>2013</v>
       </c>
-    </row>
-    <row r="8" spans="1:37">
+      <c r="AF7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
       <c r="A8">
         <v>110422</v>
       </c>
@@ -1154,8 +1178,11 @@
       <c r="AE8">
         <v>2014</v>
       </c>
-    </row>
-    <row r="9" spans="1:37">
+      <c r="AF8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
       <c r="A9">
         <v>110422</v>
       </c>
@@ -1249,8 +1276,11 @@
       <c r="AE9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="10" spans="1:37">
+      <c r="AF9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
       <c r="A10">
         <v>110422</v>
       </c>
@@ -1344,8 +1374,11 @@
       <c r="AE10">
         <v>2015</v>
       </c>
-    </row>
-    <row r="11" spans="1:37">
+      <c r="AF10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
       <c r="A11">
         <v>110422</v>
       </c>
@@ -1439,8 +1472,11 @@
       <c r="AE11">
         <v>2015</v>
       </c>
-    </row>
-    <row r="12" spans="1:37">
+      <c r="AF11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
       <c r="A12">
         <v>110422</v>
       </c>
@@ -1534,8 +1570,11 @@
       <c r="AE12">
         <v>2016</v>
       </c>
-    </row>
-    <row r="13" spans="1:37">
+      <c r="AF12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
       <c r="A13">
         <v>110422</v>
       </c>
@@ -1629,8 +1668,11 @@
       <c r="AE13">
         <v>2016</v>
       </c>
-    </row>
-    <row r="14" spans="1:37">
+      <c r="AF13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
       <c r="A14">
         <v>110422</v>
       </c>
@@ -1724,8 +1766,11 @@
       <c r="AE14">
         <v>2017</v>
       </c>
-    </row>
-    <row r="15" spans="1:37">
+      <c r="AF14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
       <c r="A15">
         <v>110422</v>
       </c>
@@ -1819,8 +1864,11 @@
       <c r="AE15">
         <v>2017</v>
       </c>
-    </row>
-    <row r="16" spans="1:37">
+      <c r="AF15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
       <c r="A16">
         <v>110422</v>
       </c>
@@ -1914,8 +1962,11 @@
       <c r="AE16">
         <v>2023</v>
       </c>
-    </row>
-    <row r="17" spans="1:37">
+      <c r="AF16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
       <c r="A17">
         <v>110422</v>
       </c>
@@ -2009,8 +2060,11 @@
       <c r="AE17">
         <v>2023</v>
       </c>
-    </row>
-    <row r="18" spans="1:37">
+      <c r="AF17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38">
       <c r="A18">
         <v>110644</v>
       </c>
@@ -2033,7 +2087,7 @@
         <v>2007</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18">
         <v>0</v>
@@ -2050,8 +2104,11 @@
       <c r="AK18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:37">
+      <c r="AL18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
       <c r="A19">
         <v>110644</v>
       </c>
@@ -2074,25 +2131,28 @@
         <v>2007</v>
       </c>
       <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AG19">
         <v>3</v>
       </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AI19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
+        <v>1</v>
+      </c>
+      <c r="AK19">
         <v>3</v>
       </c>
-      <c r="AK19">
+      <c r="AL19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:37">
+    <row r="20" spans="1:38">
       <c r="A20">
         <v>110644</v>
       </c>
@@ -2186,8 +2246,11 @@
       <c r="AE20">
         <v>2011</v>
       </c>
-    </row>
-    <row r="21" spans="1:37">
+      <c r="AF20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38">
       <c r="A21">
         <v>110644</v>
       </c>
@@ -2281,8 +2344,11 @@
       <c r="AE21">
         <v>2011</v>
       </c>
-    </row>
-    <row r="22" spans="1:37">
+      <c r="AF21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38">
       <c r="A22">
         <v>122755</v>
       </c>
@@ -2376,8 +2442,11 @@
       <c r="AE22">
         <v>2017</v>
       </c>
-    </row>
-    <row r="23" spans="1:37">
+      <c r="AF22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38">
       <c r="A23">
         <v>122755</v>
       </c>
@@ -2471,8 +2540,11 @@
       <c r="AE23">
         <v>2017</v>
       </c>
-    </row>
-    <row r="24" spans="1:37">
+      <c r="AF23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38">
       <c r="A24">
         <v>122755</v>
       </c>
@@ -2566,8 +2638,11 @@
       <c r="AE24">
         <v>2022</v>
       </c>
-    </row>
-    <row r="25" spans="1:37">
+      <c r="AF24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38">
       <c r="A25">
         <v>122755</v>
       </c>
@@ -2661,8 +2736,11 @@
       <c r="AE25">
         <v>2022</v>
       </c>
-    </row>
-    <row r="26" spans="1:37">
+      <c r="AF25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38">
       <c r="A26">
         <v>126614</v>
       </c>
@@ -2702,8 +2780,8 @@
       <c r="AE26">
         <v>2010</v>
       </c>
-      <c r="AG26">
-        <v>0</v>
+      <c r="AF26">
+        <v>1</v>
       </c>
       <c r="AH26">
         <v>0</v>
@@ -2715,10 +2793,13 @@
         <v>0</v>
       </c>
       <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:37">
+    <row r="27" spans="1:38">
       <c r="A27">
         <v>126614</v>
       </c>
@@ -2758,8 +2839,8 @@
       <c r="AE27">
         <v>2010</v>
       </c>
-      <c r="AG27">
-        <v>0</v>
+      <c r="AF27">
+        <v>2</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -2773,8 +2854,11 @@
       <c r="AK27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:37">
+      <c r="AL27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38">
       <c r="A28">
         <v>126614</v>
       </c>
@@ -2868,8 +2952,11 @@
       <c r="AE28">
         <v>2011</v>
       </c>
-    </row>
-    <row r="29" spans="1:37">
+      <c r="AF28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38">
       <c r="A29">
         <v>126614</v>
       </c>
@@ -2963,8 +3050,11 @@
       <c r="AE29">
         <v>2011</v>
       </c>
-    </row>
-    <row r="30" spans="1:37">
+      <c r="AF29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38">
       <c r="A30">
         <v>126614</v>
       </c>
@@ -3058,8 +3148,11 @@
       <c r="AE30">
         <v>2011</v>
       </c>
-    </row>
-    <row r="31" spans="1:37">
+      <c r="AF30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38">
       <c r="A31">
         <v>126614</v>
       </c>
@@ -3153,8 +3246,11 @@
       <c r="AE31">
         <v>2011</v>
       </c>
-    </row>
-    <row r="32" spans="1:37">
+      <c r="AF31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38">
       <c r="A32">
         <v>126775</v>
       </c>
@@ -3194,8 +3290,8 @@
       <c r="AE32">
         <v>2010</v>
       </c>
-      <c r="AG32">
-        <v>0</v>
+      <c r="AF32">
+        <v>1</v>
       </c>
       <c r="AH32">
         <v>0</v>
@@ -3204,13 +3300,16 @@
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK32">
+        <v>1</v>
+      </c>
+      <c r="AL32">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:37">
+    <row r="33" spans="1:38">
       <c r="A33">
         <v>126775</v>
       </c>
@@ -3250,8 +3349,8 @@
       <c r="AE33">
         <v>2010</v>
       </c>
-      <c r="AG33">
-        <v>0</v>
+      <c r="AF33">
+        <v>2</v>
       </c>
       <c r="AH33">
         <v>0</v>
@@ -3265,8 +3364,11 @@
       <c r="AK33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:37">
+      <c r="AL33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38">
       <c r="A34">
         <v>126775</v>
       </c>
@@ -3360,8 +3462,11 @@
       <c r="AE34">
         <v>2011</v>
       </c>
-    </row>
-    <row r="35" spans="1:37">
+      <c r="AF34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38">
       <c r="A35">
         <v>126775</v>
       </c>
@@ -3455,8 +3560,11 @@
       <c r="AE35">
         <v>2011</v>
       </c>
-    </row>
-    <row r="36" spans="1:37">
+      <c r="AF35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38">
       <c r="A36">
         <v>126818</v>
       </c>
@@ -3496,23 +3604,26 @@
       <c r="AE36">
         <v>2010</v>
       </c>
-      <c r="AG36">
-        <v>0</v>
+      <c r="AF36">
+        <v>1</v>
       </c>
       <c r="AH36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36">
+        <v>1</v>
+      </c>
+      <c r="AJ36">
         <v>3</v>
       </c>
-      <c r="AJ36">
-        <v>0</v>
-      </c>
       <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:37">
+    <row r="37" spans="1:38">
       <c r="A37">
         <v>126818</v>
       </c>
@@ -3552,8 +3663,8 @@
       <c r="AE37">
         <v>2010</v>
       </c>
-      <c r="AG37">
-        <v>0</v>
+      <c r="AF37">
+        <v>2</v>
       </c>
       <c r="AH37">
         <v>0</v>
@@ -3567,8 +3678,11 @@
       <c r="AK37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:37">
+      <c r="AL37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38">
       <c r="A38">
         <v>126818</v>
       </c>
@@ -3662,8 +3776,11 @@
       <c r="AE38">
         <v>2011</v>
       </c>
-    </row>
-    <row r="39" spans="1:37">
+      <c r="AF38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38">
       <c r="A39">
         <v>126818</v>
       </c>
@@ -3757,8 +3874,11 @@
       <c r="AE39">
         <v>2011</v>
       </c>
-    </row>
-    <row r="40" spans="1:37">
+      <c r="AF39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38">
       <c r="A40">
         <v>126818</v>
       </c>
@@ -3852,8 +3972,11 @@
       <c r="AE40">
         <v>2011</v>
       </c>
-    </row>
-    <row r="41" spans="1:37">
+      <c r="AF40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:38">
       <c r="A41">
         <v>126818</v>
       </c>
@@ -3947,8 +4070,11 @@
       <c r="AE41">
         <v>2011</v>
       </c>
-    </row>
-    <row r="42" spans="1:37">
+      <c r="AF41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:38">
       <c r="A42">
         <v>130943</v>
       </c>
@@ -4042,8 +4168,11 @@
       <c r="AE42">
         <v>2014</v>
       </c>
-    </row>
-    <row r="43" spans="1:37">
+      <c r="AF42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:38">
       <c r="A43">
         <v>130943</v>
       </c>
@@ -4137,8 +4266,11 @@
       <c r="AE43">
         <v>2014</v>
       </c>
-    </row>
-    <row r="44" spans="1:37">
+      <c r="AF43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38">
       <c r="A44">
         <v>131283</v>
       </c>
@@ -4232,8 +4364,11 @@
       <c r="AE44">
         <v>2016</v>
       </c>
-    </row>
-    <row r="45" spans="1:37">
+      <c r="AF44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:38">
       <c r="A45">
         <v>131283</v>
       </c>
@@ -4327,8 +4462,11 @@
       <c r="AE45">
         <v>2016</v>
       </c>
-    </row>
-    <row r="46" spans="1:37">
+      <c r="AF45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38">
       <c r="A46">
         <v>131283</v>
       </c>
@@ -4422,8 +4560,11 @@
       <c r="AE46">
         <v>2017</v>
       </c>
-    </row>
-    <row r="47" spans="1:37">
+      <c r="AF46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:38">
       <c r="A47">
         <v>131283</v>
       </c>
@@ -4517,8 +4658,11 @@
       <c r="AE47">
         <v>2017</v>
       </c>
-    </row>
-    <row r="48" spans="1:37">
+      <c r="AF47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:38">
       <c r="A48">
         <v>131496</v>
       </c>
@@ -4612,8 +4756,11 @@
       <c r="AE48">
         <v>2013</v>
       </c>
-    </row>
-    <row r="49" spans="1:31">
+      <c r="AF48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32">
       <c r="A49">
         <v>131496</v>
       </c>
@@ -4707,8 +4854,11 @@
       <c r="AE49">
         <v>2013</v>
       </c>
-    </row>
-    <row r="50" spans="1:31">
+      <c r="AF49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>132903</v>
       </c>
@@ -4802,8 +4952,11 @@
       <c r="AE50">
         <v>2017</v>
       </c>
-    </row>
-    <row r="51" spans="1:31">
+      <c r="AF50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>132903</v>
       </c>
@@ -4897,8 +5050,11 @@
       <c r="AE51">
         <v>2017</v>
       </c>
-    </row>
-    <row r="52" spans="1:31">
+      <c r="AF51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>142285</v>
       </c>
@@ -4992,8 +5148,11 @@
       <c r="AE52">
         <v>2014</v>
       </c>
-    </row>
-    <row r="53" spans="1:31">
+      <c r="AF52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32">
       <c r="A53">
         <v>142285</v>
       </c>
@@ -5087,8 +5246,11 @@
       <c r="AE53">
         <v>2014</v>
       </c>
-    </row>
-    <row r="54" spans="1:31">
+      <c r="AF53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32">
       <c r="A54">
         <v>142285</v>
       </c>
@@ -5182,8 +5344,11 @@
       <c r="AE54">
         <v>2014</v>
       </c>
-    </row>
-    <row r="55" spans="1:31">
+      <c r="AF54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:32">
       <c r="A55">
         <v>142285</v>
       </c>
@@ -5277,8 +5442,11 @@
       <c r="AE55">
         <v>2014</v>
       </c>
-    </row>
-    <row r="56" spans="1:31">
+      <c r="AF55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32">
       <c r="A56">
         <v>142285</v>
       </c>
@@ -5372,8 +5540,11 @@
       <c r="AE56">
         <v>2015</v>
       </c>
-    </row>
-    <row r="57" spans="1:31">
+      <c r="AF56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:32">
       <c r="A57">
         <v>142285</v>
       </c>
@@ -5467,8 +5638,11 @@
       <c r="AE57">
         <v>2015</v>
       </c>
-    </row>
-    <row r="58" spans="1:31">
+      <c r="AF57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:32">
       <c r="A58">
         <v>142285</v>
       </c>
@@ -5562,8 +5736,11 @@
       <c r="AE58">
         <v>2015</v>
       </c>
-    </row>
-    <row r="59" spans="1:31">
+      <c r="AF58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32">
       <c r="A59">
         <v>142285</v>
       </c>
@@ -5657,8 +5834,11 @@
       <c r="AE59">
         <v>2015</v>
       </c>
-    </row>
-    <row r="60" spans="1:31">
+      <c r="AF59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32">
       <c r="A60">
         <v>142285</v>
       </c>
@@ -5752,8 +5932,11 @@
       <c r="AE60">
         <v>2016</v>
       </c>
-    </row>
-    <row r="61" spans="1:31">
+      <c r="AF60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32">
       <c r="A61">
         <v>142285</v>
       </c>
@@ -5847,8 +6030,11 @@
       <c r="AE61">
         <v>2016</v>
       </c>
-    </row>
-    <row r="62" spans="1:31">
+      <c r="AF61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:32">
       <c r="A62">
         <v>142285</v>
       </c>
@@ -5942,8 +6128,11 @@
       <c r="AE62">
         <v>2016</v>
       </c>
-    </row>
-    <row r="63" spans="1:31">
+      <c r="AF62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:32">
       <c r="A63">
         <v>142285</v>
       </c>
@@ -6037,8 +6226,11 @@
       <c r="AE63">
         <v>2016</v>
       </c>
-    </row>
-    <row r="64" spans="1:31">
+      <c r="AF63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:32">
       <c r="A64">
         <v>142285</v>
       </c>
@@ -6132,8 +6324,11 @@
       <c r="AE64">
         <v>2017</v>
       </c>
-    </row>
-    <row r="65" spans="1:37">
+      <c r="AF64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:38">
       <c r="A65">
         <v>142285</v>
       </c>
@@ -6227,8 +6422,11 @@
       <c r="AE65">
         <v>2017</v>
       </c>
-    </row>
-    <row r="66" spans="1:37">
+      <c r="AF65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:38">
       <c r="A66">
         <v>142285</v>
       </c>
@@ -6322,8 +6520,11 @@
       <c r="AE66">
         <v>2017</v>
       </c>
-    </row>
-    <row r="67" spans="1:37">
+      <c r="AF66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:38">
       <c r="A67">
         <v>142285</v>
       </c>
@@ -6417,8 +6618,11 @@
       <c r="AE67">
         <v>2017</v>
       </c>
-    </row>
-    <row r="68" spans="1:37">
+      <c r="AF67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:38">
       <c r="A68">
         <v>144050</v>
       </c>
@@ -6441,7 +6645,7 @@
         <v>2002</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG68">
         <v>0</v>
@@ -6458,8 +6662,11 @@
       <c r="AK68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:37">
+      <c r="AL68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:38">
       <c r="A69">
         <v>144050</v>
       </c>
@@ -6482,11 +6689,11 @@
         <v>2002</v>
       </c>
       <c r="AF69">
+        <v>1</v>
+      </c>
+      <c r="AG69">
         <v>4</v>
       </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
       <c r="AH69">
         <v>0</v>
       </c>
@@ -6494,13 +6701,16 @@
         <v>0</v>
       </c>
       <c r="AJ69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK69">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:37">
+        <v>1</v>
+      </c>
+      <c r="AL69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:38">
       <c r="A70">
         <v>144050</v>
       </c>
@@ -6523,7 +6733,7 @@
         <v>2002</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG70">
         <v>0</v>
@@ -6540,8 +6750,11 @@
       <c r="AK70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:37">
+      <c r="AL70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:38">
       <c r="A71">
         <v>144050</v>
       </c>
@@ -6564,25 +6777,28 @@
         <v>2002</v>
       </c>
       <c r="AF71">
+        <v>1</v>
+      </c>
+      <c r="AG71">
         <v>6</v>
       </c>
-      <c r="AG71">
-        <v>0</v>
-      </c>
       <c r="AH71">
         <v>0</v>
       </c>
       <c r="AI71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK71">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:38">
       <c r="A72">
         <v>144050</v>
       </c>
@@ -6605,7 +6821,7 @@
         <v>2003</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -6622,8 +6838,11 @@
       <c r="AK72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:37">
+      <c r="AL72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:38">
       <c r="A73">
         <v>144050</v>
       </c>
@@ -6646,11 +6865,11 @@
         <v>2003</v>
       </c>
       <c r="AF73">
+        <v>1</v>
+      </c>
+      <c r="AG73">
         <v>6</v>
       </c>
-      <c r="AG73">
-        <v>0</v>
-      </c>
       <c r="AH73">
         <v>0</v>
       </c>
@@ -6661,10 +6880,13 @@
         <v>0</v>
       </c>
       <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:37">
+    <row r="74" spans="1:38">
       <c r="A74">
         <v>144050</v>
       </c>
@@ -6687,7 +6909,7 @@
         <v>2003</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -6704,8 +6926,11 @@
       <c r="AK74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:37">
+      <c r="AL74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:38">
       <c r="A75">
         <v>144050</v>
       </c>
@@ -6728,25 +6953,28 @@
         <v>2003</v>
       </c>
       <c r="AF75">
+        <v>1</v>
+      </c>
+      <c r="AG75">
         <v>5</v>
       </c>
-      <c r="AG75">
-        <v>0</v>
-      </c>
       <c r="AH75">
         <v>0</v>
       </c>
       <c r="AI75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:37">
+    <row r="76" spans="1:38">
       <c r="A76">
         <v>144050</v>
       </c>
@@ -6769,7 +6997,7 @@
         <v>2004</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -6786,8 +7014,11 @@
       <c r="AK76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:37">
+      <c r="AL76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:38">
       <c r="A77">
         <v>144050</v>
       </c>
@@ -6810,11 +7041,11 @@
         <v>2004</v>
       </c>
       <c r="AF77">
+        <v>1</v>
+      </c>
+      <c r="AG77">
         <v>18</v>
       </c>
-      <c r="AG77">
-        <v>0</v>
-      </c>
       <c r="AH77">
         <v>0</v>
       </c>
@@ -6825,10 +7056,13 @@
         <v>0</v>
       </c>
       <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:37">
+    <row r="78" spans="1:38">
       <c r="A78">
         <v>144050</v>
       </c>
@@ -6851,7 +7085,7 @@
         <v>2004</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -6868,8 +7102,11 @@
       <c r="AK78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:37">
+      <c r="AL78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38">
       <c r="A79">
         <v>144050</v>
       </c>
@@ -6892,25 +7129,28 @@
         <v>2004</v>
       </c>
       <c r="AF79">
+        <v>1</v>
+      </c>
+      <c r="AG79">
         <v>9</v>
       </c>
-      <c r="AG79">
-        <v>0</v>
-      </c>
       <c r="AH79">
         <v>0</v>
       </c>
       <c r="AI79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:37">
+    <row r="80" spans="1:38">
       <c r="A80">
         <v>144740</v>
       </c>
@@ -6933,7 +7173,7 @@
         <v>2002</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -6950,8 +7190,11 @@
       <c r="AK80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:37">
+      <c r="AL80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38">
       <c r="A81">
         <v>144740</v>
       </c>
@@ -6974,7 +7217,7 @@
         <v>2002</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -6991,8 +7234,11 @@
       <c r="AK81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:37">
+      <c r="AL81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38">
       <c r="A82">
         <v>144740</v>
       </c>
@@ -7015,7 +7261,7 @@
         <v>2003</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -7032,8 +7278,11 @@
       <c r="AK82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:37">
+      <c r="AL82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38">
       <c r="A83">
         <v>144740</v>
       </c>
@@ -7059,7 +7308,7 @@
         <v>1</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH83">
         <v>0</v>
@@ -7071,10 +7320,13 @@
         <v>0</v>
       </c>
       <c r="AK83">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38">
       <c r="A84">
         <v>144740</v>
       </c>
@@ -7103,7 +7355,7 @@
         <v>1</v>
       </c>
       <c r="AH84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI84">
         <v>0</v>
@@ -7112,10 +7364,13 @@
         <v>0</v>
       </c>
       <c r="AK84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38">
       <c r="A85">
         <v>144740</v>
       </c>
@@ -7138,7 +7393,7 @@
         <v>2004</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -7155,8 +7410,11 @@
       <c r="AK85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:37">
+      <c r="AL85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38">
       <c r="A86">
         <v>144740</v>
       </c>
@@ -7179,7 +7437,7 @@
         <v>2005</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -7196,8 +7454,11 @@
       <c r="AK86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:37">
+      <c r="AL86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38">
       <c r="A87">
         <v>144740</v>
       </c>
@@ -7220,7 +7481,7 @@
         <v>2005</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -7235,10 +7496,13 @@
         <v>0</v>
       </c>
       <c r="AK87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:38">
       <c r="A88">
         <v>144740</v>
       </c>
@@ -7261,7 +7525,7 @@
         <v>2006</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -7270,16 +7534,19 @@
         <v>0</v>
       </c>
       <c r="AI88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38">
       <c r="A89">
         <v>144740</v>
       </c>
@@ -7302,7 +7569,7 @@
         <v>2006</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -7319,8 +7586,11 @@
       <c r="AK89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:37">
+      <c r="AL89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38">
       <c r="A90">
         <v>144740</v>
       </c>
@@ -7363,11 +7633,62 @@
       <c r="N90">
         <v>1</v>
       </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>1</v>
+      </c>
+      <c r="S90">
+        <v>1</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90">
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <v>1</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+      <c r="Y90">
+        <v>0</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+      <c r="AA90">
+        <v>0</v>
+      </c>
+      <c r="AB90">
+        <v>0</v>
+      </c>
+      <c r="AC90">
+        <v>0</v>
+      </c>
+      <c r="AD90">
+        <v>0</v>
+      </c>
       <c r="AE90">
         <v>2009</v>
       </c>
-    </row>
-    <row r="91" spans="1:37">
+      <c r="AF90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:38">
       <c r="A91">
         <v>144740</v>
       </c>
@@ -7410,11 +7731,62 @@
       <c r="N91">
         <v>0</v>
       </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+      <c r="AA91">
+        <v>0</v>
+      </c>
+      <c r="AB91">
+        <v>0</v>
+      </c>
+      <c r="AC91">
+        <v>0</v>
+      </c>
+      <c r="AD91">
+        <v>0</v>
+      </c>
       <c r="AE91">
         <v>2009</v>
       </c>
-    </row>
-    <row r="92" spans="1:37">
+      <c r="AF91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38">
       <c r="A92">
         <v>144740</v>
       </c>
@@ -7508,8 +7880,11 @@
       <c r="AE92">
         <v>2010</v>
       </c>
-    </row>
-    <row r="93" spans="1:37">
+      <c r="AF92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38">
       <c r="A93">
         <v>144740</v>
       </c>
@@ -7603,8 +7978,11 @@
       <c r="AE93">
         <v>2010</v>
       </c>
-    </row>
-    <row r="94" spans="1:37">
+      <c r="AF93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:38">
       <c r="A94">
         <v>145600</v>
       </c>
@@ -7627,7 +8005,7 @@
         <v>2003</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -7644,8 +8022,11 @@
       <c r="AK94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:37">
+      <c r="AL94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38">
       <c r="A95">
         <v>145600</v>
       </c>
@@ -7668,25 +8049,28 @@
         <v>2003</v>
       </c>
       <c r="AF95">
+        <v>1</v>
+      </c>
+      <c r="AG95">
         <v>4</v>
       </c>
-      <c r="AG95">
-        <v>0</v>
-      </c>
       <c r="AH95">
         <v>0</v>
       </c>
       <c r="AI95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK95">
+        <v>0</v>
+      </c>
+      <c r="AL95">
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:37">
+    <row r="96" spans="1:38">
       <c r="A96">
         <v>145600</v>
       </c>
@@ -7709,7 +8093,7 @@
         <v>2003</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -7726,8 +8110,11 @@
       <c r="AK96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:37">
+      <c r="AL96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38">
       <c r="A97">
         <v>145600</v>
       </c>
@@ -7750,11 +8137,11 @@
         <v>2003</v>
       </c>
       <c r="AF97">
+        <v>1</v>
+      </c>
+      <c r="AG97">
         <v>8</v>
       </c>
-      <c r="AG97">
-        <v>0</v>
-      </c>
       <c r="AH97">
         <v>0</v>
       </c>
@@ -7765,10 +8152,13 @@
         <v>0</v>
       </c>
       <c r="AK97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38">
       <c r="A98">
         <v>145600</v>
       </c>
@@ -7791,7 +8181,7 @@
         <v>2004</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -7806,10 +8196,13 @@
         <v>0</v>
       </c>
       <c r="AK98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38">
       <c r="A99">
         <v>145600</v>
       </c>
@@ -7832,7 +8225,7 @@
         <v>2004</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG99">
         <v>0</v>
@@ -7849,8 +8242,11 @@
       <c r="AK99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:37">
+      <c r="AL99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:38">
       <c r="A100">
         <v>145600</v>
       </c>
@@ -7873,7 +8269,7 @@
         <v>2004</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG100">
         <v>0</v>
@@ -7890,8 +8286,11 @@
       <c r="AK100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:37">
+      <c r="AL100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:38">
       <c r="A101">
         <v>145600</v>
       </c>
@@ -7917,7 +8316,7 @@
         <v>1</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH101">
         <v>0</v>
@@ -7931,8 +8330,11 @@
       <c r="AK101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:37">
+      <c r="AL101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:38">
       <c r="A102">
         <v>145725</v>
       </c>
@@ -7955,7 +8357,7 @@
         <v>2003</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -7972,8 +8374,11 @@
       <c r="AK102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:37">
+      <c r="AL102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:38">
       <c r="A103">
         <v>145725</v>
       </c>
@@ -7996,7 +8401,7 @@
         <v>2003</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG103">
         <v>0</v>
@@ -8013,8 +8418,11 @@
       <c r="AK103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:37">
+      <c r="AL103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:38">
       <c r="A104">
         <v>145725</v>
       </c>
@@ -8037,7 +8445,7 @@
         <v>2003</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -8054,8 +8462,11 @@
       <c r="AK104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:37">
+      <c r="AL104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:38">
       <c r="A105">
         <v>145725</v>
       </c>
@@ -8078,25 +8489,28 @@
         <v>2003</v>
       </c>
       <c r="AF105">
+        <v>1</v>
+      </c>
+      <c r="AG105">
         <v>3</v>
       </c>
-      <c r="AG105">
-        <v>0</v>
-      </c>
       <c r="AH105">
         <v>0</v>
       </c>
       <c r="AI105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:37">
+      <c r="AL105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:38">
       <c r="A106">
         <v>145725</v>
       </c>
@@ -8119,7 +8533,7 @@
         <v>2004</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG106">
         <v>0</v>
@@ -8136,8 +8550,11 @@
       <c r="AK106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:37">
+      <c r="AL106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:38">
       <c r="A107">
         <v>145725</v>
       </c>
@@ -8160,7 +8577,7 @@
         <v>2004</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG107">
         <v>0</v>
@@ -8175,10 +8592,13 @@
         <v>0</v>
       </c>
       <c r="AK107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:38">
       <c r="A108">
         <v>145725</v>
       </c>
@@ -8201,7 +8621,7 @@
         <v>2004</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -8218,8 +8638,11 @@
       <c r="AK108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:37">
+      <c r="AL108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:38">
       <c r="A109">
         <v>145725</v>
       </c>
@@ -8242,10 +8665,10 @@
         <v>2004</v>
       </c>
       <c r="AF109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH109">
         <v>0</v>
@@ -8259,8 +8682,11 @@
       <c r="AK109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:37">
+      <c r="AL109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:38">
       <c r="A110">
         <v>146612</v>
       </c>
@@ -8354,8 +8780,11 @@
       <c r="AE110">
         <v>2016</v>
       </c>
-    </row>
-    <row r="111" spans="1:37">
+      <c r="AF110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:38">
       <c r="A111">
         <v>146612</v>
       </c>
@@ -8449,8 +8878,11 @@
       <c r="AE111">
         <v>2016</v>
       </c>
-    </row>
-    <row r="112" spans="1:37">
+      <c r="AF111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:38">
       <c r="A112">
         <v>146612</v>
       </c>
@@ -8544,8 +8976,11 @@
       <c r="AE112">
         <v>2017</v>
       </c>
-    </row>
-    <row r="113" spans="1:37">
+      <c r="AF112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:38">
       <c r="A113">
         <v>146612</v>
       </c>
@@ -8639,8 +9074,11 @@
       <c r="AE113">
         <v>2017</v>
       </c>
-    </row>
-    <row r="114" spans="1:37">
+      <c r="AF113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:38">
       <c r="A114">
         <v>147767</v>
       </c>
@@ -8663,7 +9101,7 @@
         <v>2002</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG114">
         <v>0</v>
@@ -8680,8 +9118,11 @@
       <c r="AK114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:37">
+      <c r="AL114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:38">
       <c r="A115">
         <v>147767</v>
       </c>
@@ -8704,11 +9145,11 @@
         <v>2002</v>
       </c>
       <c r="AF115">
+        <v>1</v>
+      </c>
+      <c r="AG115">
         <v>4</v>
       </c>
-      <c r="AG115">
-        <v>0</v>
-      </c>
       <c r="AH115">
         <v>0</v>
       </c>
@@ -8721,8 +9162,11 @@
       <c r="AK115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:37">
+      <c r="AL115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:38">
       <c r="A116">
         <v>147767</v>
       </c>
@@ -8745,7 +9189,7 @@
         <v>2002</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG116">
         <v>0</v>
@@ -8762,8 +9206,11 @@
       <c r="AK116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:37">
+      <c r="AL116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:38">
       <c r="A117">
         <v>147767</v>
       </c>
@@ -8786,25 +9233,28 @@
         <v>2002</v>
       </c>
       <c r="AF117">
+        <v>1</v>
+      </c>
+      <c r="AG117">
         <v>4</v>
       </c>
-      <c r="AG117">
-        <v>0</v>
-      </c>
       <c r="AH117">
         <v>0</v>
       </c>
       <c r="AI117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:38">
       <c r="A118">
         <v>149222</v>
       </c>
@@ -8827,7 +9277,7 @@
         <v>2002</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG118">
         <v>0</v>
@@ -8844,8 +9294,11 @@
       <c r="AK118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:37">
+      <c r="AL118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:38">
       <c r="A119">
         <v>149222</v>
       </c>
@@ -8871,7 +9324,7 @@
         <v>1</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH119">
         <v>0</v>
@@ -8885,8 +9338,11 @@
       <c r="AK119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:37">
+      <c r="AL119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:38">
       <c r="A120">
         <v>149222</v>
       </c>
@@ -8909,7 +9365,7 @@
         <v>2003</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG120">
         <v>0</v>
@@ -8926,8 +9382,11 @@
       <c r="AK120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:37">
+      <c r="AL120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:38">
       <c r="A121">
         <v>149222</v>
       </c>
@@ -8950,11 +9409,11 @@
         <v>2003</v>
       </c>
       <c r="AF121">
+        <v>1</v>
+      </c>
+      <c r="AG121">
         <v>4</v>
       </c>
-      <c r="AG121">
-        <v>0</v>
-      </c>
       <c r="AH121">
         <v>0</v>
       </c>
@@ -8965,10 +9424,13 @@
         <v>0</v>
       </c>
       <c r="AK121">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:38">
       <c r="A122">
         <v>149222</v>
       </c>
@@ -8991,11 +9453,11 @@
         <v>2004</v>
       </c>
       <c r="AF122">
+        <v>1</v>
+      </c>
+      <c r="AG122">
         <v>3</v>
       </c>
-      <c r="AG122">
-        <v>0</v>
-      </c>
       <c r="AH122">
         <v>0</v>
       </c>
@@ -9006,10 +9468,13 @@
         <v>0</v>
       </c>
       <c r="AK122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:38">
       <c r="A123">
         <v>149222</v>
       </c>
@@ -9032,7 +9497,7 @@
         <v>2004</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG123">
         <v>0</v>
@@ -9049,8 +9514,11 @@
       <c r="AK123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:37">
+      <c r="AL123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38">
       <c r="A124">
         <v>149222</v>
       </c>
@@ -9073,7 +9541,7 @@
         <v>2005</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG124">
         <v>0</v>
@@ -9090,8 +9558,11 @@
       <c r="AK124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:37">
+      <c r="AL124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:38">
       <c r="A125">
         <v>149222</v>
       </c>
@@ -9114,11 +9585,11 @@
         <v>2005</v>
       </c>
       <c r="AF125">
+        <v>1</v>
+      </c>
+      <c r="AG125">
         <v>6</v>
       </c>
-      <c r="AG125">
-        <v>0</v>
-      </c>
       <c r="AH125">
         <v>0</v>
       </c>
@@ -9131,8 +9602,11 @@
       <c r="AK125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:37">
+      <c r="AL125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:38">
       <c r="A126">
         <v>149222</v>
       </c>
@@ -9155,7 +9629,7 @@
         <v>2005</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG126">
         <v>0</v>
@@ -9172,8 +9646,11 @@
       <c r="AK126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:37">
+      <c r="AL126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:38">
       <c r="A127">
         <v>149222</v>
       </c>
@@ -9196,7 +9673,7 @@
         <v>2005</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG127">
         <v>0</v>
@@ -9213,8 +9690,11 @@
       <c r="AK127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:37">
+      <c r="AL127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38">
       <c r="A128">
         <v>149222</v>
       </c>
@@ -9240,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH128">
         <v>0</v>
@@ -9252,10 +9732,13 @@
         <v>0</v>
       </c>
       <c r="AK128">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:38">
       <c r="A129">
         <v>149222</v>
       </c>
@@ -9278,7 +9761,7 @@
         <v>2006</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG129">
         <v>0</v>
@@ -9295,8 +9778,11 @@
       <c r="AK129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:37">
+      <c r="AL129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:38">
       <c r="A130">
         <v>149222</v>
       </c>
@@ -9319,7 +9805,7 @@
         <v>2006</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG130">
         <v>0</v>
@@ -9336,8 +9822,11 @@
       <c r="AK130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:37">
+      <c r="AL130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:38">
       <c r="A131">
         <v>149222</v>
       </c>
@@ -9360,7 +9849,7 @@
         <v>2006</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG131">
         <v>0</v>
@@ -9377,8 +9866,11 @@
       <c r="AK131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:37">
+      <c r="AL131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:38">
       <c r="A132">
         <v>149222</v>
       </c>
@@ -9401,7 +9893,7 @@
         <v>2007</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG132">
         <v>0</v>
@@ -9418,8 +9910,11 @@
       <c r="AK132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:37">
+      <c r="AL132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:38">
       <c r="A133">
         <v>149222</v>
       </c>
@@ -9445,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH133">
         <v>0</v>
@@ -9457,10 +9952,13 @@
         <v>0</v>
       </c>
       <c r="AK133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:38">
       <c r="A134">
         <v>149222</v>
       </c>
@@ -9483,7 +9981,7 @@
         <v>2007</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG134">
         <v>0</v>
@@ -9500,8 +9998,11 @@
       <c r="AK134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:37">
+      <c r="AL134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:38">
       <c r="A135">
         <v>149222</v>
       </c>
@@ -9524,7 +10025,7 @@
         <v>2007</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG135">
         <v>0</v>
@@ -9541,8 +10042,11 @@
       <c r="AK135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:37">
+      <c r="AL135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:38">
       <c r="A136">
         <v>149222</v>
       </c>
@@ -9561,17 +10065,26 @@
       <c r="F136">
         <v>0</v>
       </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
       <c r="N136">
         <v>1</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>1</v>
+      </c>
+      <c r="AB136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
       </c>
       <c r="AE136">
         <v>2008</v>
       </c>
-      <c r="AG136">
-        <v>0</v>
+      <c r="AF136">
+        <v>1</v>
       </c>
       <c r="AH136">
         <v>0</v>
@@ -9585,8 +10098,11 @@
       <c r="AK136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:37">
+      <c r="AL136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:38">
       <c r="A137">
         <v>149222</v>
       </c>
@@ -9605,17 +10121,26 @@
       <c r="F137">
         <v>0</v>
       </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
       <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
         <v>0</v>
       </c>
       <c r="AE137">
         <v>2008</v>
       </c>
-      <c r="AG137">
-        <v>0</v>
+      <c r="AF137">
+        <v>2</v>
       </c>
       <c r="AH137">
         <v>0</v>
@@ -9629,8 +10154,11 @@
       <c r="AK137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:37">
+      <c r="AL137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:38">
       <c r="A138">
         <v>149222</v>
       </c>
@@ -9649,17 +10177,26 @@
       <c r="F138">
         <v>1</v>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
       <c r="N138">
         <v>2</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>1</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>1</v>
       </c>
       <c r="AE138">
         <v>2008</v>
       </c>
-      <c r="AG138">
-        <v>0</v>
+      <c r="AF138">
+        <v>1</v>
       </c>
       <c r="AH138">
         <v>0</v>
@@ -9673,8 +10210,11 @@
       <c r="AK138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:37">
+      <c r="AL138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:38">
       <c r="A139">
         <v>149222</v>
       </c>
@@ -9693,17 +10233,26 @@
       <c r="F139">
         <v>0</v>
       </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
       <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
         <v>0</v>
       </c>
       <c r="AE139">
         <v>2008</v>
       </c>
-      <c r="AG139">
-        <v>0</v>
+      <c r="AF139">
+        <v>2</v>
       </c>
       <c r="AH139">
         <v>0</v>
@@ -9717,8 +10266,11 @@
       <c r="AK139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:37">
+      <c r="AL139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:38">
       <c r="A140">
         <v>149222</v>
       </c>
@@ -9743,11 +10295,23 @@
       <c r="N140">
         <v>0</v>
       </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="V140">
+        <v>0</v>
+      </c>
+      <c r="AB140">
+        <v>0</v>
+      </c>
+      <c r="AD140">
+        <v>0</v>
+      </c>
       <c r="AE140">
         <v>2009</v>
       </c>
-      <c r="AG140">
-        <v>0</v>
+      <c r="AF140">
+        <v>2</v>
       </c>
       <c r="AH140">
         <v>0</v>
@@ -9761,8 +10325,11 @@
       <c r="AK140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:37">
+      <c r="AL140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:38">
       <c r="A141">
         <v>149222</v>
       </c>
@@ -9787,11 +10354,23 @@
       <c r="N141">
         <v>5</v>
       </c>
+      <c r="T141">
+        <v>0</v>
+      </c>
+      <c r="V141">
+        <v>5</v>
+      </c>
+      <c r="AB141">
+        <v>1</v>
+      </c>
+      <c r="AD141">
+        <v>0</v>
+      </c>
       <c r="AE141">
         <v>2009</v>
       </c>
-      <c r="AG141">
-        <v>0</v>
+      <c r="AF141">
+        <v>1</v>
       </c>
       <c r="AH141">
         <v>0</v>
@@ -9803,10 +10382,13 @@
         <v>0</v>
       </c>
       <c r="AK141">
+        <v>0</v>
+      </c>
+      <c r="AL141">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:37">
+    <row r="142" spans="1:38">
       <c r="A142">
         <v>149222</v>
       </c>
@@ -9831,11 +10413,23 @@
       <c r="N142">
         <v>0</v>
       </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+      <c r="V142">
+        <v>0</v>
+      </c>
+      <c r="AB142">
+        <v>0</v>
+      </c>
+      <c r="AD142">
+        <v>0</v>
+      </c>
       <c r="AE142">
         <v>2009</v>
       </c>
-      <c r="AG142">
-        <v>0</v>
+      <c r="AF142">
+        <v>1</v>
       </c>
       <c r="AH142">
         <v>0</v>
@@ -9849,8 +10443,11 @@
       <c r="AK142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:37">
+      <c r="AL142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:38">
       <c r="A143">
         <v>149222</v>
       </c>
@@ -9875,11 +10472,23 @@
       <c r="N143">
         <v>0</v>
       </c>
+      <c r="T143">
+        <v>0</v>
+      </c>
+      <c r="V143">
+        <v>0</v>
+      </c>
+      <c r="AB143">
+        <v>0</v>
+      </c>
+      <c r="AD143">
+        <v>0</v>
+      </c>
       <c r="AE143">
         <v>2009</v>
       </c>
-      <c r="AG143">
-        <v>0</v>
+      <c r="AF143">
+        <v>2</v>
       </c>
       <c r="AH143">
         <v>0</v>
@@ -9893,8 +10502,11 @@
       <c r="AK143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:37">
+      <c r="AL143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:38">
       <c r="A144">
         <v>149222</v>
       </c>
@@ -9988,8 +10600,11 @@
       <c r="AE144">
         <v>2010</v>
       </c>
-    </row>
-    <row r="145" spans="1:37">
+      <c r="AF144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:38">
       <c r="A145">
         <v>149222</v>
       </c>
@@ -10083,8 +10698,11 @@
       <c r="AE145">
         <v>2010</v>
       </c>
-    </row>
-    <row r="146" spans="1:37">
+      <c r="AF145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:38">
       <c r="A146">
         <v>149222</v>
       </c>
@@ -10178,8 +10796,11 @@
       <c r="AE146">
         <v>2010</v>
       </c>
-    </row>
-    <row r="147" spans="1:37">
+      <c r="AF146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:38">
       <c r="A147">
         <v>149222</v>
       </c>
@@ -10273,8 +10894,11 @@
       <c r="AE147">
         <v>2010</v>
       </c>
-    </row>
-    <row r="148" spans="1:37">
+      <c r="AF147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:38">
       <c r="A148">
         <v>149222</v>
       </c>
@@ -10368,8 +10992,11 @@
       <c r="AE148">
         <v>2011</v>
       </c>
-    </row>
-    <row r="149" spans="1:37">
+      <c r="AF148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:38">
       <c r="A149">
         <v>149222</v>
       </c>
@@ -10463,8 +11090,11 @@
       <c r="AE149">
         <v>2011</v>
       </c>
-    </row>
-    <row r="150" spans="1:37">
+      <c r="AF149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:38">
       <c r="A150">
         <v>149222</v>
       </c>
@@ -10558,8 +11188,11 @@
       <c r="AE150">
         <v>2011</v>
       </c>
-    </row>
-    <row r="151" spans="1:37">
+      <c r="AF150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:38">
       <c r="A151">
         <v>149222</v>
       </c>
@@ -10653,8 +11286,11 @@
       <c r="AE151">
         <v>2011</v>
       </c>
-    </row>
-    <row r="152" spans="1:37">
+      <c r="AF151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:38">
       <c r="A152">
         <v>149772</v>
       </c>
@@ -10677,7 +11313,7 @@
         <v>2002</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG152">
         <v>0</v>
@@ -10694,8 +11330,11 @@
       <c r="AK152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:37">
+      <c r="AL152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:38">
       <c r="A153">
         <v>149772</v>
       </c>
@@ -10718,11 +11357,11 @@
         <v>2002</v>
       </c>
       <c r="AF153">
+        <v>1</v>
+      </c>
+      <c r="AG153">
         <v>8</v>
       </c>
-      <c r="AG153">
-        <v>0</v>
-      </c>
       <c r="AH153">
         <v>0</v>
       </c>
@@ -10735,8 +11374,11 @@
       <c r="AK153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:37">
+      <c r="AL153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:38">
       <c r="A154">
         <v>150136</v>
       </c>
@@ -10830,8 +11472,11 @@
       <c r="AE154">
         <v>2016</v>
       </c>
-    </row>
-    <row r="155" spans="1:37">
+      <c r="AF154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:38">
       <c r="A155">
         <v>150136</v>
       </c>
@@ -10925,8 +11570,11 @@
       <c r="AE155">
         <v>2016</v>
       </c>
-    </row>
-    <row r="156" spans="1:37">
+      <c r="AF155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:38">
       <c r="A156">
         <v>151111</v>
       </c>
@@ -10948,8 +11596,11 @@
       <c r="AE156">
         <v>2001</v>
       </c>
-    </row>
-    <row r="157" spans="1:37">
+      <c r="AF156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:38">
       <c r="A157">
         <v>151111</v>
       </c>
@@ -10971,8 +11622,11 @@
       <c r="AE157">
         <v>2001</v>
       </c>
-    </row>
-    <row r="158" spans="1:37">
+      <c r="AF157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:38">
       <c r="A158">
         <v>153603</v>
       </c>
@@ -10995,7 +11649,7 @@
         <v>2004</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG158">
         <v>0</v>
@@ -11012,8 +11666,11 @@
       <c r="AK158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:37">
+      <c r="AL158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:38">
       <c r="A159">
         <v>153603</v>
       </c>
@@ -11036,7 +11693,7 @@
         <v>2004</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG159">
         <v>0</v>
@@ -11045,16 +11702,19 @@
         <v>0</v>
       </c>
       <c r="AI159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:38">
       <c r="A160">
         <v>153603</v>
       </c>
@@ -11077,7 +11737,7 @@
         <v>2004</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG160">
         <v>0</v>
@@ -11094,8 +11754,11 @@
       <c r="AK160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:37">
+      <c r="AL160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:38">
       <c r="A161">
         <v>153603</v>
       </c>
@@ -11118,7 +11781,7 @@
         <v>2004</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG161">
         <v>0</v>
@@ -11135,8 +11798,11 @@
       <c r="AK161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:37">
+      <c r="AL161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:38">
       <c r="A162">
         <v>153603</v>
       </c>
@@ -11159,7 +11825,7 @@
         <v>2005</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG162">
         <v>0</v>
@@ -11176,8 +11842,11 @@
       <c r="AK162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:37">
+      <c r="AL162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:38">
       <c r="A163">
         <v>153603</v>
       </c>
@@ -11200,7 +11869,7 @@
         <v>2005</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG163">
         <v>0</v>
@@ -11215,10 +11884,13 @@
         <v>0</v>
       </c>
       <c r="AK163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:38">
       <c r="A164">
         <v>153603</v>
       </c>
@@ -11241,7 +11913,7 @@
         <v>2005</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -11258,8 +11930,11 @@
       <c r="AK164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:37">
+      <c r="AL164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:38">
       <c r="A165">
         <v>153603</v>
       </c>
@@ -11282,7 +11957,7 @@
         <v>2005</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG165">
         <v>0</v>
@@ -11299,8 +11974,11 @@
       <c r="AK165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:37">
+      <c r="AL165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:38">
       <c r="A166">
         <v>153603</v>
       </c>
@@ -11323,7 +12001,7 @@
         <v>2006</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG166">
         <v>0</v>
@@ -11340,8 +12018,11 @@
       <c r="AK166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:37">
+      <c r="AL166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:38">
       <c r="A167">
         <v>153603</v>
       </c>
@@ -11364,7 +12045,7 @@
         <v>2006</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG167">
         <v>0</v>
@@ -11381,8 +12062,11 @@
       <c r="AK167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:37">
+      <c r="AL167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:38">
       <c r="A168">
         <v>153603</v>
       </c>
@@ -11405,7 +12089,7 @@
         <v>2006</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG168">
         <v>0</v>
@@ -11422,8 +12106,11 @@
       <c r="AK168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:37">
+      <c r="AL168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:38">
       <c r="A169">
         <v>153603</v>
       </c>
@@ -11446,7 +12133,7 @@
         <v>2006</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG169">
         <v>0</v>
@@ -11463,8 +12150,11 @@
       <c r="AK169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:37">
+      <c r="AL169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:38">
       <c r="A170">
         <v>153603</v>
       </c>
@@ -11487,7 +12177,7 @@
         <v>2007</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG170">
         <v>0</v>
@@ -11504,8 +12194,11 @@
       <c r="AK170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:37">
+      <c r="AL170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:38">
       <c r="A171">
         <v>153603</v>
       </c>
@@ -11528,7 +12221,7 @@
         <v>2007</v>
       </c>
       <c r="AF171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG171">
         <v>0</v>
@@ -11545,8 +12238,11 @@
       <c r="AK171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:37">
+      <c r="AL171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:38">
       <c r="A172">
         <v>153603</v>
       </c>
@@ -11569,7 +12265,7 @@
         <v>2007</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -11586,8 +12282,11 @@
       <c r="AK172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:37">
+      <c r="AL172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:38">
       <c r="A173">
         <v>153603</v>
       </c>
@@ -11613,7 +12312,7 @@
         <v>1</v>
       </c>
       <c r="AG173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH173">
         <v>0</v>
@@ -11627,8 +12326,11 @@
       <c r="AK173">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:37">
+      <c r="AL173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:38">
       <c r="A174">
         <v>153603</v>
       </c>
@@ -11647,17 +12349,26 @@
       <c r="F174">
         <v>0</v>
       </c>
-      <c r="G174">
-        <v>0</v>
-      </c>
       <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="T174">
+        <v>0</v>
+      </c>
+      <c r="V174">
+        <v>0</v>
+      </c>
+      <c r="AB174">
+        <v>0</v>
+      </c>
+      <c r="AD174">
         <v>0</v>
       </c>
       <c r="AE174">
         <v>2008</v>
       </c>
-      <c r="AG174">
-        <v>0</v>
+      <c r="AF174">
+        <v>2</v>
       </c>
       <c r="AH174">
         <v>0</v>
@@ -11671,8 +12382,11 @@
       <c r="AK174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:37">
+      <c r="AL174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:38">
       <c r="A175">
         <v>153603</v>
       </c>
@@ -11691,17 +12405,26 @@
       <c r="F175">
         <v>0</v>
       </c>
-      <c r="G175">
-        <v>0</v>
-      </c>
       <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="T175">
+        <v>0</v>
+      </c>
+      <c r="V175">
+        <v>0</v>
+      </c>
+      <c r="AB175">
+        <v>0</v>
+      </c>
+      <c r="AD175">
         <v>0</v>
       </c>
       <c r="AE175">
         <v>2008</v>
       </c>
-      <c r="AG175">
-        <v>0</v>
+      <c r="AF175">
+        <v>1</v>
       </c>
       <c r="AH175">
         <v>0</v>
@@ -11715,8 +12438,11 @@
       <c r="AK175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:37">
+      <c r="AL175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:38">
       <c r="A176">
         <v>153603</v>
       </c>
@@ -11735,17 +12461,26 @@
       <c r="F176">
         <v>0</v>
       </c>
-      <c r="G176">
-        <v>0</v>
-      </c>
       <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="T176">
+        <v>0</v>
+      </c>
+      <c r="V176">
+        <v>0</v>
+      </c>
+      <c r="AB176">
+        <v>0</v>
+      </c>
+      <c r="AD176">
         <v>0</v>
       </c>
       <c r="AE176">
         <v>2008</v>
       </c>
-      <c r="AG176">
-        <v>0</v>
+      <c r="AF176">
+        <v>1</v>
       </c>
       <c r="AH176">
         <v>0</v>
@@ -11757,10 +12492,13 @@
         <v>0</v>
       </c>
       <c r="AK176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:38">
       <c r="A177">
         <v>153603</v>
       </c>
@@ -11779,17 +12517,26 @@
       <c r="F177">
         <v>0</v>
       </c>
-      <c r="G177">
-        <v>0</v>
-      </c>
       <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="T177">
+        <v>0</v>
+      </c>
+      <c r="V177">
+        <v>0</v>
+      </c>
+      <c r="AB177">
+        <v>0</v>
+      </c>
+      <c r="AD177">
         <v>0</v>
       </c>
       <c r="AE177">
         <v>2008</v>
       </c>
-      <c r="AG177">
-        <v>0</v>
+      <c r="AF177">
+        <v>2</v>
       </c>
       <c r="AH177">
         <v>0</v>
@@ -11803,8 +12550,11 @@
       <c r="AK177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:37">
+      <c r="AL177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:38">
       <c r="A178">
         <v>153658</v>
       </c>
@@ -11898,8 +12648,11 @@
       <c r="AE178">
         <v>2013</v>
       </c>
-    </row>
-    <row r="179" spans="1:37">
+      <c r="AF178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:38">
       <c r="A179">
         <v>153658</v>
       </c>
@@ -11993,8 +12746,11 @@
       <c r="AE179">
         <v>2013</v>
       </c>
-    </row>
-    <row r="180" spans="1:37">
+      <c r="AF179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:38">
       <c r="A180">
         <v>153658</v>
       </c>
@@ -12088,8 +12844,11 @@
       <c r="AE180">
         <v>2014</v>
       </c>
-    </row>
-    <row r="181" spans="1:37">
+      <c r="AF180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:38">
       <c r="A181">
         <v>153658</v>
       </c>
@@ -12183,8 +12942,11 @@
       <c r="AE181">
         <v>2014</v>
       </c>
-    </row>
-    <row r="182" spans="1:37">
+      <c r="AF181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:38">
       <c r="A182">
         <v>161253</v>
       </c>
@@ -12278,8 +13040,11 @@
       <c r="AE182">
         <v>2012</v>
       </c>
-    </row>
-    <row r="183" spans="1:37">
+      <c r="AF182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:38">
       <c r="A183">
         <v>161253</v>
       </c>
@@ -12373,8 +13138,11 @@
       <c r="AE183">
         <v>2012</v>
       </c>
-    </row>
-    <row r="184" spans="1:37">
+      <c r="AF183">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:38">
       <c r="A184">
         <v>161253</v>
       </c>
@@ -12468,8 +13236,11 @@
       <c r="AE184">
         <v>2013</v>
       </c>
-    </row>
-    <row r="185" spans="1:37">
+      <c r="AF184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:38">
       <c r="A185">
         <v>161253</v>
       </c>
@@ -12563,8 +13334,11 @@
       <c r="AE185">
         <v>2013</v>
       </c>
-    </row>
-    <row r="186" spans="1:37">
+      <c r="AF185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:38">
       <c r="A186">
         <v>161253</v>
       </c>
@@ -12658,8 +13432,11 @@
       <c r="AE186">
         <v>2014</v>
       </c>
-    </row>
-    <row r="187" spans="1:37">
+      <c r="AF186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:38">
       <c r="A187">
         <v>161253</v>
       </c>
@@ -12753,8 +13530,11 @@
       <c r="AE187">
         <v>2014</v>
       </c>
-    </row>
-    <row r="188" spans="1:37">
+      <c r="AF187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:38">
       <c r="A188">
         <v>161253</v>
       </c>
@@ -12848,8 +13628,11 @@
       <c r="AE188">
         <v>2015</v>
       </c>
-    </row>
-    <row r="189" spans="1:37">
+      <c r="AF188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:38">
       <c r="A189">
         <v>161253</v>
       </c>
@@ -12943,8 +13726,11 @@
       <c r="AE189">
         <v>2015</v>
       </c>
-    </row>
-    <row r="190" spans="1:37">
+      <c r="AF189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:38">
       <c r="A190">
         <v>161253</v>
       </c>
@@ -13038,8 +13824,11 @@
       <c r="AE190">
         <v>2016</v>
       </c>
-    </row>
-    <row r="191" spans="1:37">
+      <c r="AF190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:38">
       <c r="A191">
         <v>161253</v>
       </c>
@@ -13133,8 +13922,11 @@
       <c r="AE191">
         <v>2016</v>
       </c>
-    </row>
-    <row r="192" spans="1:37">
+      <c r="AF191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:38">
       <c r="A192">
         <v>161253</v>
       </c>
@@ -13228,8 +14020,11 @@
       <c r="AE192">
         <v>2017</v>
       </c>
-    </row>
-    <row r="193" spans="1:37">
+      <c r="AF192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:38">
       <c r="A193">
         <v>161253</v>
       </c>
@@ -13323,8 +14118,11 @@
       <c r="AE193">
         <v>2017</v>
       </c>
-    </row>
-    <row r="194" spans="1:37">
+      <c r="AF193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:38">
       <c r="A194">
         <v>167987</v>
       </c>
@@ -13418,8 +14216,11 @@
       <c r="AE194">
         <v>2016</v>
       </c>
-    </row>
-    <row r="195" spans="1:37">
+      <c r="AF194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:38">
       <c r="A195">
         <v>167987</v>
       </c>
@@ -13513,8 +14314,11 @@
       <c r="AE195">
         <v>2016</v>
       </c>
-    </row>
-    <row r="196" spans="1:37">
+      <c r="AF195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:38">
       <c r="A196">
         <v>170976</v>
       </c>
@@ -13536,8 +14340,11 @@
       <c r="AE196">
         <v>2001</v>
       </c>
-    </row>
-    <row r="197" spans="1:37">
+      <c r="AF196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:38">
       <c r="A197">
         <v>170976</v>
       </c>
@@ -13559,8 +14366,11 @@
       <c r="AE197">
         <v>2001</v>
       </c>
-    </row>
-    <row r="198" spans="1:37">
+      <c r="AF197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:38">
       <c r="A198">
         <v>171100</v>
       </c>
@@ -13654,8 +14464,11 @@
       <c r="AE198">
         <v>2022</v>
       </c>
-    </row>
-    <row r="199" spans="1:37">
+      <c r="AF198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:38">
       <c r="A199">
         <v>171100</v>
       </c>
@@ -13749,8 +14562,11 @@
       <c r="AE199">
         <v>2022</v>
       </c>
-    </row>
-    <row r="200" spans="1:37">
+      <c r="AF199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:38">
       <c r="A200">
         <v>171100</v>
       </c>
@@ -13844,8 +14660,11 @@
       <c r="AE200">
         <v>2023</v>
       </c>
-    </row>
-    <row r="201" spans="1:37">
+      <c r="AF200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:38">
       <c r="A201">
         <v>171100</v>
       </c>
@@ -13939,8 +14758,11 @@
       <c r="AE201">
         <v>2023</v>
       </c>
-    </row>
-    <row r="202" spans="1:37">
+      <c r="AF201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:38">
       <c r="A202">
         <v>174233</v>
       </c>
@@ -14034,8 +14856,11 @@
       <c r="AE202">
         <v>2018</v>
       </c>
-    </row>
-    <row r="203" spans="1:37">
+      <c r="AF202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:38">
       <c r="A203">
         <v>174233</v>
       </c>
@@ -14129,8 +14954,11 @@
       <c r="AE203">
         <v>2018</v>
       </c>
-    </row>
-    <row r="204" spans="1:37">
+      <c r="AF203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:38">
       <c r="A204">
         <v>190664</v>
       </c>
@@ -14224,8 +15052,11 @@
       <c r="AE204">
         <v>2016</v>
       </c>
-    </row>
-    <row r="205" spans="1:37">
+      <c r="AF204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:38">
       <c r="A205">
         <v>190664</v>
       </c>
@@ -14319,8 +15150,11 @@
       <c r="AE205">
         <v>2016</v>
       </c>
-    </row>
-    <row r="206" spans="1:37">
+      <c r="AF205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:38">
       <c r="A206">
         <v>190664</v>
       </c>
@@ -14414,8 +15248,11 @@
       <c r="AE206">
         <v>2017</v>
       </c>
-    </row>
-    <row r="207" spans="1:37">
+      <c r="AF206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:38">
       <c r="A207">
         <v>190664</v>
       </c>
@@ -14509,8 +15346,11 @@
       <c r="AE207">
         <v>2017</v>
       </c>
-    </row>
-    <row r="208" spans="1:37">
+      <c r="AF207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:38">
       <c r="A208">
         <v>195030</v>
       </c>
@@ -14533,10 +15373,10 @@
         <v>2003</v>
       </c>
       <c r="AF208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG208">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH208">
         <v>0</v>
@@ -14548,10 +15388,13 @@
         <v>0</v>
       </c>
       <c r="AK208">
+        <v>0</v>
+      </c>
+      <c r="AL208">
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:37">
+    <row r="209" spans="1:38">
       <c r="A209">
         <v>195030</v>
       </c>
@@ -14574,10 +15417,10 @@
         <v>2003</v>
       </c>
       <c r="AF209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH209">
         <v>0</v>
@@ -14591,8 +15434,11 @@
       <c r="AK209">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:37">
+      <c r="AL209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:38">
       <c r="A210">
         <v>195030</v>
       </c>
@@ -14615,7 +15461,7 @@
         <v>2004</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG210">
         <v>0</v>
@@ -14632,8 +15478,11 @@
       <c r="AK210">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:37">
+      <c r="AL210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:38">
       <c r="A211">
         <v>195030</v>
       </c>
@@ -14656,11 +15505,11 @@
         <v>2004</v>
       </c>
       <c r="AF211">
+        <v>1</v>
+      </c>
+      <c r="AG211">
         <v>6</v>
       </c>
-      <c r="AG211">
-        <v>0</v>
-      </c>
       <c r="AH211">
         <v>0</v>
       </c>
@@ -14671,10 +15520,13 @@
         <v>0</v>
       </c>
       <c r="AK211">
+        <v>0</v>
+      </c>
+      <c r="AL211">
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:37">
+    <row r="212" spans="1:38">
       <c r="A212">
         <v>195030</v>
       </c>
@@ -14697,11 +15549,11 @@
         <v>2005</v>
       </c>
       <c r="AF212">
+        <v>1</v>
+      </c>
+      <c r="AG212">
         <v>16</v>
       </c>
-      <c r="AG212">
-        <v>0</v>
-      </c>
       <c r="AH212">
         <v>0</v>
       </c>
@@ -14712,10 +15564,13 @@
         <v>0</v>
       </c>
       <c r="AK212">
+        <v>0</v>
+      </c>
+      <c r="AL212">
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:37">
+    <row r="213" spans="1:38">
       <c r="A213">
         <v>195030</v>
       </c>
@@ -14738,7 +15593,7 @@
         <v>2005</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -14755,8 +15610,11 @@
       <c r="AK213">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:37">
+      <c r="AL213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:38">
       <c r="A214">
         <v>195030</v>
       </c>
@@ -14775,17 +15633,26 @@
       <c r="F214">
         <v>0</v>
       </c>
-      <c r="G214">
-        <v>0</v>
-      </c>
       <c r="N214">
+        <v>0</v>
+      </c>
+      <c r="T214">
+        <v>0</v>
+      </c>
+      <c r="V214">
+        <v>0</v>
+      </c>
+      <c r="AB214">
+        <v>0</v>
+      </c>
+      <c r="AD214">
         <v>0</v>
       </c>
       <c r="AE214">
         <v>2008</v>
       </c>
-      <c r="AG214">
-        <v>0</v>
+      <c r="AF214">
+        <v>2</v>
       </c>
       <c r="AH214">
         <v>0</v>
@@ -14797,10 +15664,13 @@
         <v>0</v>
       </c>
       <c r="AK214">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:38">
       <c r="A215">
         <v>195030</v>
       </c>
@@ -14819,32 +15689,44 @@
       <c r="F215">
         <v>5</v>
       </c>
-      <c r="G215">
-        <v>0</v>
-      </c>
       <c r="N215">
         <v>10</v>
       </c>
+      <c r="T215">
+        <v>0</v>
+      </c>
+      <c r="V215">
+        <v>7</v>
+      </c>
+      <c r="AB215">
+        <v>0</v>
+      </c>
+      <c r="AD215">
+        <v>3</v>
+      </c>
       <c r="AE215">
         <v>2008</v>
       </c>
-      <c r="AG215">
+      <c r="AF215">
         <v>1</v>
       </c>
       <c r="AH215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI215">
         <v>0</v>
       </c>
       <c r="AJ215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK215">
+        <v>1</v>
+      </c>
+      <c r="AL215">
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:37">
+    <row r="216" spans="1:38">
       <c r="A216">
         <v>195030</v>
       </c>
@@ -14869,26 +15751,41 @@
       <c r="N216">
         <v>8</v>
       </c>
+      <c r="T216">
+        <v>0</v>
+      </c>
+      <c r="V216">
+        <v>6</v>
+      </c>
+      <c r="AB216">
+        <v>1</v>
+      </c>
+      <c r="AD216">
+        <v>2</v>
+      </c>
       <c r="AE216">
         <v>2009</v>
       </c>
-      <c r="AG216">
-        <v>0</v>
+      <c r="AF216">
+        <v>1</v>
       </c>
       <c r="AH216">
         <v>0</v>
       </c>
       <c r="AI216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ216">
         <v>1</v>
       </c>
       <c r="AK216">
+        <v>1</v>
+      </c>
+      <c r="AL216">
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:37">
+    <row r="217" spans="1:38">
       <c r="A217">
         <v>195030</v>
       </c>
@@ -14913,11 +15810,23 @@
       <c r="N217">
         <v>0</v>
       </c>
+      <c r="T217">
+        <v>0</v>
+      </c>
+      <c r="V217">
+        <v>0</v>
+      </c>
+      <c r="AB217">
+        <v>0</v>
+      </c>
+      <c r="AD217">
+        <v>0</v>
+      </c>
       <c r="AE217">
         <v>2009</v>
       </c>
-      <c r="AG217">
-        <v>0</v>
+      <c r="AF217">
+        <v>2</v>
       </c>
       <c r="AH217">
         <v>0</v>
@@ -14929,10 +15838,13 @@
         <v>0</v>
       </c>
       <c r="AK217">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:38">
       <c r="A218">
         <v>195030</v>
       </c>
@@ -15026,8 +15938,11 @@
       <c r="AE218">
         <v>2011</v>
       </c>
-    </row>
-    <row r="219" spans="1:37">
+      <c r="AF218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:38">
       <c r="A219">
         <v>195030</v>
       </c>
@@ -15121,8 +16036,11 @@
       <c r="AE219">
         <v>2011</v>
       </c>
-    </row>
-    <row r="220" spans="1:37">
+      <c r="AF219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:38">
       <c r="A220">
         <v>195030</v>
       </c>
@@ -15216,8 +16134,11 @@
       <c r="AE220">
         <v>2012</v>
       </c>
-    </row>
-    <row r="221" spans="1:37">
+      <c r="AF220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:38">
       <c r="A221">
         <v>195030</v>
       </c>
@@ -15311,8 +16232,11 @@
       <c r="AE221">
         <v>2012</v>
       </c>
-    </row>
-    <row r="222" spans="1:37">
+      <c r="AF221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:38">
       <c r="A222">
         <v>195030</v>
       </c>
@@ -15406,8 +16330,11 @@
       <c r="AE222">
         <v>2013</v>
       </c>
-    </row>
-    <row r="223" spans="1:37">
+      <c r="AF222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:38">
       <c r="A223">
         <v>195030</v>
       </c>
@@ -15501,8 +16428,11 @@
       <c r="AE223">
         <v>2013</v>
       </c>
-    </row>
-    <row r="224" spans="1:37">
+      <c r="AF223">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:38">
       <c r="A224">
         <v>195030</v>
       </c>
@@ -15596,8 +16526,11 @@
       <c r="AE224">
         <v>2014</v>
       </c>
-    </row>
-    <row r="225" spans="1:31">
+      <c r="AF224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:32">
       <c r="A225">
         <v>195030</v>
       </c>
@@ -15691,8 +16624,11 @@
       <c r="AE225">
         <v>2014</v>
       </c>
-    </row>
-    <row r="226" spans="1:31">
+      <c r="AF225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:32">
       <c r="A226">
         <v>195030</v>
       </c>
@@ -15786,8 +16722,11 @@
       <c r="AE226">
         <v>2015</v>
       </c>
-    </row>
-    <row r="227" spans="1:31">
+      <c r="AF226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:32">
       <c r="A227">
         <v>195030</v>
       </c>
@@ -15881,8 +16820,11 @@
       <c r="AE227">
         <v>2015</v>
       </c>
-    </row>
-    <row r="228" spans="1:31">
+      <c r="AF227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:32">
       <c r="A228">
         <v>195030</v>
       </c>
@@ -15976,8 +16918,11 @@
       <c r="AE228">
         <v>2016</v>
       </c>
-    </row>
-    <row r="229" spans="1:31">
+      <c r="AF228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:32">
       <c r="A229">
         <v>195030</v>
       </c>
@@ -16071,8 +17016,11 @@
       <c r="AE229">
         <v>2016</v>
       </c>
-    </row>
-    <row r="230" spans="1:31">
+      <c r="AF229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:32">
       <c r="A230">
         <v>195030</v>
       </c>
@@ -16166,8 +17114,11 @@
       <c r="AE230">
         <v>2017</v>
       </c>
-    </row>
-    <row r="231" spans="1:31">
+      <c r="AF230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:32">
       <c r="A231">
         <v>195030</v>
       </c>
@@ -16261,8 +17212,11 @@
       <c r="AE231">
         <v>2017</v>
       </c>
-    </row>
-    <row r="232" spans="1:31">
+      <c r="AF231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:32">
       <c r="A232">
         <v>196088</v>
       </c>
@@ -16356,8 +17310,11 @@
       <c r="AE232">
         <v>2020</v>
       </c>
-    </row>
-    <row r="233" spans="1:31">
+      <c r="AF232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:32">
       <c r="A233">
         <v>196088</v>
       </c>
@@ -16451,8 +17408,11 @@
       <c r="AE233">
         <v>2020</v>
       </c>
-    </row>
-    <row r="234" spans="1:31">
+      <c r="AF233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:32">
       <c r="A234">
         <v>197869</v>
       </c>
@@ -16546,8 +17506,11 @@
       <c r="AE234">
         <v>2013</v>
       </c>
-    </row>
-    <row r="235" spans="1:31">
+      <c r="AF234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:32">
       <c r="A235">
         <v>197869</v>
       </c>
@@ -16641,8 +17604,11 @@
       <c r="AE235">
         <v>2013</v>
       </c>
-    </row>
-    <row r="236" spans="1:31">
+      <c r="AF235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:32">
       <c r="A236">
         <v>197869</v>
       </c>
@@ -16736,8 +17702,11 @@
       <c r="AE236">
         <v>2014</v>
       </c>
-    </row>
-    <row r="237" spans="1:31">
+      <c r="AF236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:32">
       <c r="A237">
         <v>197869</v>
       </c>
@@ -16831,8 +17800,11 @@
       <c r="AE237">
         <v>2014</v>
       </c>
-    </row>
-    <row r="238" spans="1:31">
+      <c r="AF237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:32">
       <c r="A238">
         <v>197869</v>
       </c>
@@ -16926,8 +17898,11 @@
       <c r="AE238">
         <v>2017</v>
       </c>
-    </row>
-    <row r="239" spans="1:31">
+      <c r="AF238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:32">
       <c r="A239">
         <v>197869</v>
       </c>
@@ -17021,8 +17996,11 @@
       <c r="AE239">
         <v>2017</v>
       </c>
-    </row>
-    <row r="240" spans="1:31">
+      <c r="AF239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:32">
       <c r="A240">
         <v>198464</v>
       </c>
@@ -17116,8 +18094,11 @@
       <c r="AE240">
         <v>2017</v>
       </c>
-    </row>
-    <row r="241" spans="1:31">
+      <c r="AF240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:32">
       <c r="A241">
         <v>198464</v>
       </c>
@@ -17211,8 +18192,11 @@
       <c r="AE241">
         <v>2017</v>
       </c>
-    </row>
-    <row r="242" spans="1:31">
+      <c r="AF241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:32">
       <c r="A242">
         <v>199102</v>
       </c>
@@ -17306,8 +18290,11 @@
       <c r="AE242">
         <v>2017</v>
       </c>
-    </row>
-    <row r="243" spans="1:31">
+      <c r="AF242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:32">
       <c r="A243">
         <v>199102</v>
       </c>
@@ -17401,8 +18388,11 @@
       <c r="AE243">
         <v>2017</v>
       </c>
-    </row>
-    <row r="244" spans="1:31">
+      <c r="AF243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:32">
       <c r="A244">
         <v>199120</v>
       </c>
@@ -17496,8 +18486,11 @@
       <c r="AE244">
         <v>2017</v>
       </c>
-    </row>
-    <row r="245" spans="1:31">
+      <c r="AF244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:32">
       <c r="A245">
         <v>199120</v>
       </c>
@@ -17591,8 +18584,11 @@
       <c r="AE245">
         <v>2017</v>
       </c>
-    </row>
-    <row r="246" spans="1:31">
+      <c r="AF245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:32">
       <c r="A246">
         <v>199120</v>
       </c>
@@ -17686,8 +18682,11 @@
       <c r="AE246">
         <v>2017</v>
       </c>
-    </row>
-    <row r="247" spans="1:31">
+      <c r="AF246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:32">
       <c r="A247">
         <v>199120</v>
       </c>
@@ -17781,8 +18780,11 @@
       <c r="AE247">
         <v>2017</v>
       </c>
-    </row>
-    <row r="248" spans="1:31">
+      <c r="AF247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:32">
       <c r="A248">
         <v>199139</v>
       </c>
@@ -17876,8 +18878,11 @@
       <c r="AE248">
         <v>2017</v>
       </c>
-    </row>
-    <row r="249" spans="1:31">
+      <c r="AF248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:32">
       <c r="A249">
         <v>199139</v>
       </c>
@@ -17971,8 +18976,11 @@
       <c r="AE249">
         <v>2017</v>
       </c>
-    </row>
-    <row r="250" spans="1:31">
+      <c r="AF249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:32">
       <c r="A250">
         <v>199157</v>
       </c>
@@ -18066,8 +19074,11 @@
       <c r="AE250">
         <v>2017</v>
       </c>
-    </row>
-    <row r="251" spans="1:31">
+      <c r="AF250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:32">
       <c r="A251">
         <v>199157</v>
       </c>
@@ -18161,8 +19172,11 @@
       <c r="AE251">
         <v>2017</v>
       </c>
-    </row>
-    <row r="252" spans="1:31">
+      <c r="AF251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:32">
       <c r="A252">
         <v>199193</v>
       </c>
@@ -18256,8 +19270,11 @@
       <c r="AE252">
         <v>2017</v>
       </c>
-    </row>
-    <row r="253" spans="1:31">
+      <c r="AF252">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:32">
       <c r="A253">
         <v>199193</v>
       </c>
@@ -18351,8 +19368,11 @@
       <c r="AE253">
         <v>2017</v>
       </c>
-    </row>
-    <row r="254" spans="1:31">
+      <c r="AF253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:32">
       <c r="A254">
         <v>199193</v>
       </c>
@@ -18446,8 +19466,11 @@
       <c r="AE254">
         <v>2017</v>
       </c>
-    </row>
-    <row r="255" spans="1:31">
+      <c r="AF254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:32">
       <c r="A255">
         <v>199193</v>
       </c>
@@ -18541,8 +19564,11 @@
       <c r="AE255">
         <v>2017</v>
       </c>
-    </row>
-    <row r="256" spans="1:31">
+      <c r="AF255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:32">
       <c r="A256">
         <v>206084</v>
       </c>
@@ -18564,8 +19590,11 @@
       <c r="AE256">
         <v>2001</v>
       </c>
-    </row>
-    <row r="257" spans="1:37">
+      <c r="AF256">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:38">
       <c r="A257">
         <v>206084</v>
       </c>
@@ -18587,8 +19616,11 @@
       <c r="AE257">
         <v>2001</v>
       </c>
-    </row>
-    <row r="258" spans="1:37">
+      <c r="AF257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:38">
       <c r="A258">
         <v>206084</v>
       </c>
@@ -18610,8 +19642,11 @@
       <c r="AE258">
         <v>2001</v>
       </c>
-    </row>
-    <row r="259" spans="1:37">
+      <c r="AF258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:38">
       <c r="A259">
         <v>206084</v>
       </c>
@@ -18633,8 +19668,11 @@
       <c r="AE259">
         <v>2001</v>
       </c>
-    </row>
-    <row r="260" spans="1:37">
+      <c r="AF259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:38">
       <c r="A260">
         <v>206084</v>
       </c>
@@ -18659,11 +19697,23 @@
       <c r="N260">
         <v>0</v>
       </c>
+      <c r="T260">
+        <v>0</v>
+      </c>
+      <c r="V260">
+        <v>0</v>
+      </c>
+      <c r="AB260">
+        <v>0</v>
+      </c>
+      <c r="AD260">
+        <v>0</v>
+      </c>
       <c r="AE260">
         <v>2009</v>
       </c>
-      <c r="AG260">
-        <v>0</v>
+      <c r="AF260">
+        <v>1</v>
       </c>
       <c r="AH260">
         <v>0</v>
@@ -18675,10 +19725,13 @@
         <v>0</v>
       </c>
       <c r="AK260">
+        <v>0</v>
+      </c>
+      <c r="AL260">
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:37">
+    <row r="261" spans="1:38">
       <c r="A261">
         <v>206084</v>
       </c>
@@ -18703,11 +19756,23 @@
       <c r="N261">
         <v>0</v>
       </c>
+      <c r="T261">
+        <v>0</v>
+      </c>
+      <c r="V261">
+        <v>0</v>
+      </c>
+      <c r="AB261">
+        <v>0</v>
+      </c>
+      <c r="AD261">
+        <v>0</v>
+      </c>
       <c r="AE261">
         <v>2009</v>
       </c>
-      <c r="AG261">
-        <v>0</v>
+      <c r="AF261">
+        <v>2</v>
       </c>
       <c r="AH261">
         <v>0</v>
@@ -18719,10 +19784,13 @@
         <v>0</v>
       </c>
       <c r="AK261">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="262" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:38">
       <c r="A262">
         <v>206084</v>
       </c>
@@ -18816,8 +19884,11 @@
       <c r="AE262">
         <v>2010</v>
       </c>
-    </row>
-    <row r="263" spans="1:37">
+      <c r="AF262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:38">
       <c r="A263">
         <v>206084</v>
       </c>
@@ -18911,8 +19982,11 @@
       <c r="AE263">
         <v>2010</v>
       </c>
-    </row>
-    <row r="264" spans="1:37">
+      <c r="AF263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:38">
       <c r="A264">
         <v>206084</v>
       </c>
@@ -19006,8 +20080,11 @@
       <c r="AE264">
         <v>2011</v>
       </c>
-    </row>
-    <row r="265" spans="1:37">
+      <c r="AF264">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:38">
       <c r="A265">
         <v>206084</v>
       </c>
@@ -19101,8 +20178,11 @@
       <c r="AE265">
         <v>2011</v>
       </c>
-    </row>
-    <row r="266" spans="1:37">
+      <c r="AF265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:38">
       <c r="A266">
         <v>206084</v>
       </c>
@@ -19196,8 +20276,11 @@
       <c r="AE266">
         <v>2012</v>
       </c>
-    </row>
-    <row r="267" spans="1:37">
+      <c r="AF266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:38">
       <c r="A267">
         <v>206084</v>
       </c>
@@ -19291,8 +20374,11 @@
       <c r="AE267">
         <v>2012</v>
       </c>
-    </row>
-    <row r="268" spans="1:37">
+      <c r="AF267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:38">
       <c r="A268">
         <v>206084</v>
       </c>
@@ -19386,8 +20472,11 @@
       <c r="AE268">
         <v>2013</v>
       </c>
-    </row>
-    <row r="269" spans="1:37">
+      <c r="AF268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:38">
       <c r="A269">
         <v>206084</v>
       </c>
@@ -19481,8 +20570,11 @@
       <c r="AE269">
         <v>2013</v>
       </c>
-    </row>
-    <row r="270" spans="1:37">
+      <c r="AF269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:38">
       <c r="A270">
         <v>206084</v>
       </c>
@@ -19576,8 +20668,11 @@
       <c r="AE270">
         <v>2014</v>
       </c>
-    </row>
-    <row r="271" spans="1:37">
+      <c r="AF270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:38">
       <c r="A271">
         <v>206084</v>
       </c>
@@ -19671,8 +20766,11 @@
       <c r="AE271">
         <v>2014</v>
       </c>
-    </row>
-    <row r="272" spans="1:37">
+      <c r="AF271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:38">
       <c r="A272">
         <v>206084</v>
       </c>
@@ -19766,8 +20864,11 @@
       <c r="AE272">
         <v>2015</v>
       </c>
-    </row>
-    <row r="273" spans="1:37">
+      <c r="AF272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:38">
       <c r="A273">
         <v>206084</v>
       </c>
@@ -19861,8 +20962,11 @@
       <c r="AE273">
         <v>2015</v>
       </c>
-    </row>
-    <row r="274" spans="1:37">
+      <c r="AF273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:38">
       <c r="A274">
         <v>206084</v>
       </c>
@@ -19956,8 +21060,11 @@
       <c r="AE274">
         <v>2016</v>
       </c>
-    </row>
-    <row r="275" spans="1:37">
+      <c r="AF274">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:38">
       <c r="A275">
         <v>206084</v>
       </c>
@@ -20051,8 +21158,11 @@
       <c r="AE275">
         <v>2016</v>
       </c>
-    </row>
-    <row r="276" spans="1:37">
+      <c r="AF275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:38">
       <c r="A276">
         <v>206084</v>
       </c>
@@ -20146,8 +21256,11 @@
       <c r="AE276">
         <v>2017</v>
       </c>
-    </row>
-    <row r="277" spans="1:37">
+      <c r="AF276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:38">
       <c r="A277">
         <v>206084</v>
       </c>
@@ -20241,8 +21354,11 @@
       <c r="AE277">
         <v>2017</v>
       </c>
-    </row>
-    <row r="278" spans="1:37">
+      <c r="AF277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:38">
       <c r="A278">
         <v>206941</v>
       </c>
@@ -20265,7 +21381,7 @@
         <v>2004</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG278">
         <v>0</v>
@@ -20282,8 +21398,11 @@
       <c r="AK278">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:37">
+      <c r="AL278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:38">
       <c r="A279">
         <v>206941</v>
       </c>
@@ -20306,11 +21425,11 @@
         <v>2004</v>
       </c>
       <c r="AF279">
+        <v>1</v>
+      </c>
+      <c r="AG279">
         <v>5</v>
       </c>
-      <c r="AG279">
-        <v>0</v>
-      </c>
       <c r="AH279">
         <v>0</v>
       </c>
@@ -20323,8 +21442,11 @@
       <c r="AK279">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:37">
+      <c r="AL279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:38">
       <c r="A280">
         <v>206941</v>
       </c>
@@ -20347,7 +21469,7 @@
         <v>2006</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG280">
         <v>0</v>
@@ -20359,13 +21481,16 @@
         <v>0</v>
       </c>
       <c r="AJ280">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK280">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="281" spans="1:37">
+        <v>1</v>
+      </c>
+      <c r="AL280">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:38">
       <c r="A281">
         <v>206941</v>
       </c>
@@ -20388,7 +21513,7 @@
         <v>2006</v>
       </c>
       <c r="AF281">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG281">
         <v>0</v>
@@ -20405,8 +21530,11 @@
       <c r="AK281">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:37">
+      <c r="AL281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:38">
       <c r="A282">
         <v>207388</v>
       </c>
@@ -20429,11 +21557,11 @@
         <v>2006</v>
       </c>
       <c r="AF282">
+        <v>1</v>
+      </c>
+      <c r="AG282">
         <v>3</v>
       </c>
-      <c r="AG282">
-        <v>0</v>
-      </c>
       <c r="AH282">
         <v>0</v>
       </c>
@@ -20444,10 +21572,13 @@
         <v>0</v>
       </c>
       <c r="AK282">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="283" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL282">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:38">
       <c r="A283">
         <v>207388</v>
       </c>
@@ -20470,7 +21601,7 @@
         <v>2006</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG283">
         <v>0</v>
@@ -20487,8 +21618,11 @@
       <c r="AK283">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:37">
+      <c r="AL283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:38">
       <c r="A284">
         <v>207388</v>
       </c>
@@ -20511,10 +21645,10 @@
         <v>2006</v>
       </c>
       <c r="AF284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH284">
         <v>0</v>
@@ -20526,10 +21660,13 @@
         <v>0</v>
       </c>
       <c r="AK284">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="285" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL284">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:38">
       <c r="A285">
         <v>207388</v>
       </c>
@@ -20552,7 +21689,7 @@
         <v>2006</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG285">
         <v>0</v>
@@ -20569,8 +21706,11 @@
       <c r="AK285">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:37">
+      <c r="AL285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:38">
       <c r="A286">
         <v>207500</v>
       </c>
@@ -20593,10 +21733,10 @@
         <v>2002</v>
       </c>
       <c r="AF286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH286">
         <v>0</v>
@@ -20610,8 +21750,11 @@
       <c r="AK286">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:37">
+      <c r="AL286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:38">
       <c r="A287">
         <v>207500</v>
       </c>
@@ -20634,7 +21777,7 @@
         <v>2002</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG287">
         <v>0</v>
@@ -20651,8 +21794,11 @@
       <c r="AK287">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:37">
+      <c r="AL287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:38">
       <c r="A288">
         <v>207500</v>
       </c>
@@ -20675,7 +21821,7 @@
         <v>2002</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG288">
         <v>0</v>
@@ -20690,10 +21836,13 @@
         <v>0</v>
       </c>
       <c r="AK288">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="289" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL288">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:38">
       <c r="A289">
         <v>207500</v>
       </c>
@@ -20716,7 +21865,7 @@
         <v>2002</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG289">
         <v>0</v>
@@ -20733,8 +21882,11 @@
       <c r="AK289">
         <v>0</v>
       </c>
-    </row>
-    <row r="290" spans="1:37">
+      <c r="AL289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:38">
       <c r="A290">
         <v>207500</v>
       </c>
@@ -20757,7 +21909,7 @@
         <v>2003</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG290">
         <v>0</v>
@@ -20774,8 +21926,11 @@
       <c r="AK290">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:37">
+      <c r="AL290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:38">
       <c r="A291">
         <v>207500</v>
       </c>
@@ -20801,22 +21956,25 @@
         <v>1</v>
       </c>
       <c r="AG291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ291">
         <v>0</v>
       </c>
       <c r="AK291">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="292" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:38">
       <c r="A292">
         <v>207500</v>
       </c>
@@ -20839,7 +21997,7 @@
         <v>2003</v>
       </c>
       <c r="AF292">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG292">
         <v>0</v>
@@ -20856,8 +22014,11 @@
       <c r="AK292">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:37">
+      <c r="AL292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:38">
       <c r="A293">
         <v>207500</v>
       </c>
@@ -20880,7 +22041,7 @@
         <v>2003</v>
       </c>
       <c r="AF293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG293">
         <v>0</v>
@@ -20895,10 +22056,13 @@
         <v>0</v>
       </c>
       <c r="AK293">
+        <v>0</v>
+      </c>
+      <c r="AL293">
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:37">
+    <row r="294" spans="1:38">
       <c r="A294">
         <v>207500</v>
       </c>
@@ -20921,7 +22085,7 @@
         <v>2004</v>
       </c>
       <c r="AF294">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG294">
         <v>0</v>
@@ -20938,8 +22102,11 @@
       <c r="AK294">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:37">
+      <c r="AL294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:38">
       <c r="A295">
         <v>207500</v>
       </c>
@@ -20962,7 +22129,7 @@
         <v>2004</v>
       </c>
       <c r="AF295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG295">
         <v>0</v>
@@ -20977,10 +22144,13 @@
         <v>0</v>
       </c>
       <c r="AK295">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:38">
       <c r="A296">
         <v>207500</v>
       </c>
@@ -21003,7 +22173,7 @@
         <v>2004</v>
       </c>
       <c r="AF296">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG296">
         <v>0</v>
@@ -21020,8 +22190,11 @@
       <c r="AK296">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:37">
+      <c r="AL296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:38">
       <c r="A297">
         <v>207500</v>
       </c>
@@ -21047,22 +22220,25 @@
         <v>1</v>
       </c>
       <c r="AG297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ297">
         <v>0</v>
       </c>
       <c r="AK297">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:38">
       <c r="A298">
         <v>207500</v>
       </c>
@@ -21085,7 +22261,7 @@
         <v>2005</v>
       </c>
       <c r="AF298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG298">
         <v>0</v>
@@ -21102,8 +22278,11 @@
       <c r="AK298">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:37">
+      <c r="AL298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:38">
       <c r="A299">
         <v>207500</v>
       </c>
@@ -21126,25 +22305,28 @@
         <v>2005</v>
       </c>
       <c r="AF299">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG299">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ299">
         <v>0</v>
       </c>
       <c r="AK299">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:38">
       <c r="A300">
         <v>207500</v>
       </c>
@@ -21167,7 +22349,7 @@
         <v>2005</v>
       </c>
       <c r="AF300">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG300">
         <v>0</v>
@@ -21184,8 +22366,11 @@
       <c r="AK300">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:37">
+      <c r="AL300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:38">
       <c r="A301">
         <v>207500</v>
       </c>
@@ -21208,11 +22393,11 @@
         <v>2005</v>
       </c>
       <c r="AF301">
+        <v>1</v>
+      </c>
+      <c r="AG301">
         <v>3</v>
       </c>
-      <c r="AG301">
-        <v>0</v>
-      </c>
       <c r="AH301">
         <v>0</v>
       </c>
@@ -21223,10 +22408,13 @@
         <v>0</v>
       </c>
       <c r="AK301">
+        <v>0</v>
+      </c>
+      <c r="AL301">
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:37">
+    <row r="302" spans="1:38">
       <c r="A302">
         <v>207500</v>
       </c>
@@ -21249,13 +22437,13 @@
         <v>2006</v>
       </c>
       <c r="AF302">
+        <v>1</v>
+      </c>
+      <c r="AG302">
         <v>4</v>
       </c>
-      <c r="AG302">
-        <v>1</v>
-      </c>
       <c r="AH302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI302">
         <v>0</v>
@@ -21264,10 +22452,13 @@
         <v>0</v>
       </c>
       <c r="AK302">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="303" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL302">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:38">
       <c r="A303">
         <v>207500</v>
       </c>
@@ -21290,7 +22481,7 @@
         <v>2006</v>
       </c>
       <c r="AF303">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG303">
         <v>0</v>
@@ -21307,8 +22498,11 @@
       <c r="AK303">
         <v>0</v>
       </c>
-    </row>
-    <row r="304" spans="1:37">
+      <c r="AL303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:38">
       <c r="A304">
         <v>207500</v>
       </c>
@@ -21331,7 +22525,7 @@
         <v>2006</v>
       </c>
       <c r="AF304">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG304">
         <v>0</v>
@@ -21348,8 +22542,11 @@
       <c r="AK304">
         <v>0</v>
       </c>
-    </row>
-    <row r="305" spans="1:37">
+      <c r="AL304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:38">
       <c r="A305">
         <v>207500</v>
       </c>
@@ -21372,25 +22569,28 @@
         <v>2006</v>
       </c>
       <c r="AF305">
+        <v>1</v>
+      </c>
+      <c r="AG305">
         <v>3</v>
       </c>
-      <c r="AG305">
-        <v>0</v>
-      </c>
       <c r="AH305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ305">
         <v>0</v>
       </c>
       <c r="AK305">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:38">
       <c r="A306">
         <v>213020</v>
       </c>
@@ -21484,8 +22684,11 @@
       <c r="AE306">
         <v>2015</v>
       </c>
-    </row>
-    <row r="307" spans="1:37">
+      <c r="AF306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:38">
       <c r="A307">
         <v>213020</v>
       </c>
@@ -21579,8 +22782,11 @@
       <c r="AE307">
         <v>2015</v>
       </c>
-    </row>
-    <row r="308" spans="1:37">
+      <c r="AF307">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:38">
       <c r="A308">
         <v>213020</v>
       </c>
@@ -21674,8 +22880,11 @@
       <c r="AE308">
         <v>2016</v>
       </c>
-    </row>
-    <row r="309" spans="1:37">
+      <c r="AF308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:38">
       <c r="A309">
         <v>213020</v>
       </c>
@@ -21769,8 +22978,11 @@
       <c r="AE309">
         <v>2016</v>
       </c>
-    </row>
-    <row r="310" spans="1:37">
+      <c r="AF309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:38">
       <c r="A310">
         <v>213020</v>
       </c>
@@ -21864,8 +23076,11 @@
       <c r="AE310">
         <v>2017</v>
       </c>
-    </row>
-    <row r="311" spans="1:37">
+      <c r="AF310">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:38">
       <c r="A311">
         <v>213020</v>
       </c>
@@ -21959,8 +23174,11 @@
       <c r="AE311">
         <v>2017</v>
       </c>
-    </row>
-    <row r="312" spans="1:37">
+      <c r="AF311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:38">
       <c r="A312">
         <v>215062</v>
       </c>
@@ -22054,8 +23272,11 @@
       <c r="AE312">
         <v>2023</v>
       </c>
-    </row>
-    <row r="313" spans="1:37">
+      <c r="AF312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:38">
       <c r="A313">
         <v>215062</v>
       </c>
@@ -22149,8 +23370,11 @@
       <c r="AE313">
         <v>2023</v>
       </c>
-    </row>
-    <row r="314" spans="1:37">
+      <c r="AF313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:38">
       <c r="A314">
         <v>216038</v>
       </c>
@@ -22173,7 +23397,7 @@
         <v>2006</v>
       </c>
       <c r="AF314">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG314">
         <v>0</v>
@@ -22188,10 +23412,13 @@
         <v>0</v>
       </c>
       <c r="AK314">
+        <v>0</v>
+      </c>
+      <c r="AL314">
         <v>24</v>
       </c>
     </row>
-    <row r="315" spans="1:37">
+    <row r="315" spans="1:38">
       <c r="A315">
         <v>216038</v>
       </c>
@@ -22214,7 +23441,7 @@
         <v>2006</v>
       </c>
       <c r="AF315">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG315">
         <v>0</v>
@@ -22229,10 +23456,13 @@
         <v>0</v>
       </c>
       <c r="AK315">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:38">
       <c r="A316">
         <v>221999</v>
       </c>
@@ -22254,8 +23484,11 @@
       <c r="AE316">
         <v>2001</v>
       </c>
-    </row>
-    <row r="317" spans="1:37">
+      <c r="AF316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:38">
       <c r="A317">
         <v>221999</v>
       </c>
@@ -22277,8 +23510,11 @@
       <c r="AE317">
         <v>2001</v>
       </c>
-    </row>
-    <row r="318" spans="1:37">
+      <c r="AF317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:38">
       <c r="A318">
         <v>221999</v>
       </c>
@@ -22300,8 +23536,11 @@
       <c r="AE318">
         <v>2001</v>
       </c>
-    </row>
-    <row r="319" spans="1:37">
+      <c r="AF318">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:38">
       <c r="A319">
         <v>221999</v>
       </c>
@@ -22323,8 +23562,11 @@
       <c r="AE319">
         <v>2001</v>
       </c>
-    </row>
-    <row r="320" spans="1:37">
+      <c r="AF319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:38">
       <c r="A320">
         <v>221999</v>
       </c>
@@ -22347,10 +23589,10 @@
         <v>2002</v>
       </c>
       <c r="AF320">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH320">
         <v>0</v>
@@ -22364,8 +23606,11 @@
       <c r="AK320">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:37">
+      <c r="AL320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:38">
       <c r="A321">
         <v>221999</v>
       </c>
@@ -22388,7 +23633,7 @@
         <v>2002</v>
       </c>
       <c r="AF321">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG321">
         <v>0</v>
@@ -22405,8 +23650,11 @@
       <c r="AK321">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:37">
+      <c r="AL321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:38">
       <c r="A322">
         <v>221999</v>
       </c>
@@ -22429,7 +23677,7 @@
         <v>2002</v>
       </c>
       <c r="AF322">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG322">
         <v>0</v>
@@ -22446,8 +23694,11 @@
       <c r="AK322">
         <v>0</v>
       </c>
-    </row>
-    <row r="323" spans="1:37">
+      <c r="AL322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:38">
       <c r="A323">
         <v>221999</v>
       </c>
@@ -22470,11 +23721,11 @@
         <v>2002</v>
       </c>
       <c r="AF323">
+        <v>1</v>
+      </c>
+      <c r="AG323">
         <v>4</v>
       </c>
-      <c r="AG323">
-        <v>0</v>
-      </c>
       <c r="AH323">
         <v>0</v>
       </c>
@@ -22485,10 +23736,13 @@
         <v>0</v>
       </c>
       <c r="AK323">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="324" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL323">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="324" spans="1:38">
       <c r="A324">
         <v>221999</v>
       </c>
@@ -22511,7 +23765,7 @@
         <v>2003</v>
       </c>
       <c r="AF324">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG324">
         <v>0</v>
@@ -22526,10 +23780,13 @@
         <v>0</v>
       </c>
       <c r="AK324">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:38">
       <c r="A325">
         <v>221999</v>
       </c>
@@ -22552,7 +23809,7 @@
         <v>2003</v>
       </c>
       <c r="AF325">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG325">
         <v>0</v>
@@ -22569,8 +23826,11 @@
       <c r="AK325">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:37">
+      <c r="AL325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:38">
       <c r="A326">
         <v>221999</v>
       </c>
@@ -22593,7 +23853,7 @@
         <v>2003</v>
       </c>
       <c r="AF326">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG326">
         <v>0</v>
@@ -22610,8 +23870,11 @@
       <c r="AK326">
         <v>0</v>
       </c>
-    </row>
-    <row r="327" spans="1:37">
+      <c r="AL326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:38">
       <c r="A327">
         <v>221999</v>
       </c>
@@ -22634,11 +23897,11 @@
         <v>2003</v>
       </c>
       <c r="AF327">
+        <v>1</v>
+      </c>
+      <c r="AG327">
         <v>3</v>
       </c>
-      <c r="AG327">
-        <v>0</v>
-      </c>
       <c r="AH327">
         <v>0</v>
       </c>
@@ -22649,10 +23912,13 @@
         <v>0</v>
       </c>
       <c r="AK327">
+        <v>0</v>
+      </c>
+      <c r="AL327">
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:37">
+    <row r="328" spans="1:38">
       <c r="A328">
         <v>221999</v>
       </c>
@@ -22675,7 +23941,7 @@
         <v>2004</v>
       </c>
       <c r="AF328">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG328">
         <v>0</v>
@@ -22692,8 +23958,11 @@
       <c r="AK328">
         <v>0</v>
       </c>
-    </row>
-    <row r="329" spans="1:37">
+      <c r="AL328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:38">
       <c r="A329">
         <v>221999</v>
       </c>
@@ -22716,7 +23985,7 @@
         <v>2004</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG329">
         <v>0</v>
@@ -22731,10 +24000,13 @@
         <v>0</v>
       </c>
       <c r="AK329">
+        <v>0</v>
+      </c>
+      <c r="AL329">
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:37">
+    <row r="330" spans="1:38">
       <c r="A330">
         <v>221999</v>
       </c>
@@ -22757,7 +24029,7 @@
         <v>2004</v>
       </c>
       <c r="AF330">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG330">
         <v>0</v>
@@ -22774,8 +24046,11 @@
       <c r="AK330">
         <v>0</v>
       </c>
-    </row>
-    <row r="331" spans="1:37">
+      <c r="AL330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:38">
       <c r="A331">
         <v>221999</v>
       </c>
@@ -22798,11 +24073,11 @@
         <v>2004</v>
       </c>
       <c r="AF331">
+        <v>1</v>
+      </c>
+      <c r="AG331">
         <v>5</v>
       </c>
-      <c r="AG331">
-        <v>0</v>
-      </c>
       <c r="AH331">
         <v>0</v>
       </c>
@@ -22813,10 +24088,13 @@
         <v>0</v>
       </c>
       <c r="AK331">
+        <v>0</v>
+      </c>
+      <c r="AL331">
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:37">
+    <row r="332" spans="1:38">
       <c r="A332">
         <v>221999</v>
       </c>
@@ -22839,7 +24117,7 @@
         <v>2005</v>
       </c>
       <c r="AF332">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG332">
         <v>0</v>
@@ -22856,8 +24134,11 @@
       <c r="AK332">
         <v>0</v>
       </c>
-    </row>
-    <row r="333" spans="1:37">
+      <c r="AL332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:38">
       <c r="A333">
         <v>221999</v>
       </c>
@@ -22883,7 +24164,7 @@
         <v>1</v>
       </c>
       <c r="AG333">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH333">
         <v>0</v>
@@ -22897,8 +24178,11 @@
       <c r="AK333">
         <v>0</v>
       </c>
-    </row>
-    <row r="334" spans="1:37">
+      <c r="AL333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:38">
       <c r="A334">
         <v>221999</v>
       </c>
@@ -22921,7 +24205,7 @@
         <v>2005</v>
       </c>
       <c r="AF334">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG334">
         <v>0</v>
@@ -22938,8 +24222,11 @@
       <c r="AK334">
         <v>0</v>
       </c>
-    </row>
-    <row r="335" spans="1:37">
+      <c r="AL334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:38">
       <c r="A335">
         <v>221999</v>
       </c>
@@ -22965,22 +24252,25 @@
         <v>1</v>
       </c>
       <c r="AG335">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH335">
         <v>0</v>
       </c>
       <c r="AI335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ335">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK335">
         <v>0</v>
       </c>
-    </row>
-    <row r="336" spans="1:37">
+      <c r="AL335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:38">
       <c r="A336">
         <v>221999</v>
       </c>
@@ -23003,11 +24293,11 @@
         <v>2006</v>
       </c>
       <c r="AF336">
+        <v>1</v>
+      </c>
+      <c r="AG336">
         <v>3</v>
       </c>
-      <c r="AG336">
-        <v>0</v>
-      </c>
       <c r="AH336">
         <v>0</v>
       </c>
@@ -23018,10 +24308,13 @@
         <v>0</v>
       </c>
       <c r="AK336">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="337" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL336">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:38">
       <c r="A337">
         <v>221999</v>
       </c>
@@ -23044,7 +24337,7 @@
         <v>2006</v>
       </c>
       <c r="AF337">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG337">
         <v>0</v>
@@ -23061,8 +24354,11 @@
       <c r="AK337">
         <v>0</v>
       </c>
-    </row>
-    <row r="338" spans="1:37">
+      <c r="AL337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:38">
       <c r="A338">
         <v>221999</v>
       </c>
@@ -23085,11 +24381,11 @@
         <v>2006</v>
       </c>
       <c r="AF338">
+        <v>1</v>
+      </c>
+      <c r="AG338">
         <v>3</v>
       </c>
-      <c r="AG338">
-        <v>0</v>
-      </c>
       <c r="AH338">
         <v>0</v>
       </c>
@@ -23102,8 +24398,11 @@
       <c r="AK338">
         <v>0</v>
       </c>
-    </row>
-    <row r="339" spans="1:37">
+      <c r="AL338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:38">
       <c r="A339">
         <v>221999</v>
       </c>
@@ -23126,7 +24425,7 @@
         <v>2006</v>
       </c>
       <c r="AF339">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG339">
         <v>0</v>
@@ -23143,8 +24442,11 @@
       <c r="AK339">
         <v>0</v>
       </c>
-    </row>
-    <row r="340" spans="1:37">
+      <c r="AL339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:38">
       <c r="A340">
         <v>221999</v>
       </c>
@@ -23167,7 +24469,7 @@
         <v>2007</v>
       </c>
       <c r="AF340">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG340">
         <v>0</v>
@@ -23184,8 +24486,11 @@
       <c r="AK340">
         <v>0</v>
       </c>
-    </row>
-    <row r="341" spans="1:37">
+      <c r="AL340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:38">
       <c r="A341">
         <v>221999</v>
       </c>
@@ -23208,11 +24513,11 @@
         <v>2007</v>
       </c>
       <c r="AF341">
+        <v>1</v>
+      </c>
+      <c r="AG341">
         <v>3</v>
       </c>
-      <c r="AG341">
-        <v>0</v>
-      </c>
       <c r="AH341">
         <v>0</v>
       </c>
@@ -23220,13 +24525,16 @@
         <v>0</v>
       </c>
       <c r="AJ341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK341">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="342" spans="1:37">
+        <v>1</v>
+      </c>
+      <c r="AL341">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="342" spans="1:38">
       <c r="A342">
         <v>221999</v>
       </c>
@@ -23249,7 +24557,7 @@
         <v>2007</v>
       </c>
       <c r="AF342">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG342">
         <v>0</v>
@@ -23266,8 +24574,11 @@
       <c r="AK342">
         <v>0</v>
       </c>
-    </row>
-    <row r="343" spans="1:37">
+      <c r="AL342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:38">
       <c r="A343">
         <v>221999</v>
       </c>
@@ -23290,11 +24601,11 @@
         <v>2007</v>
       </c>
       <c r="AF343">
+        <v>1</v>
+      </c>
+      <c r="AG343">
         <v>3</v>
       </c>
-      <c r="AG343">
-        <v>0</v>
-      </c>
       <c r="AH343">
         <v>0</v>
       </c>
@@ -23305,10 +24616,13 @@
         <v>0</v>
       </c>
       <c r="AK343">
+        <v>0</v>
+      </c>
+      <c r="AL343">
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:37">
+    <row r="344" spans="1:38">
       <c r="A344">
         <v>221999</v>
       </c>
@@ -23327,17 +24641,26 @@
       <c r="F344">
         <v>3</v>
       </c>
-      <c r="G344">
-        <v>1</v>
-      </c>
       <c r="N344">
         <v>5</v>
       </c>
+      <c r="T344">
+        <v>1</v>
+      </c>
+      <c r="V344">
+        <v>3</v>
+      </c>
+      <c r="AB344">
+        <v>0</v>
+      </c>
+      <c r="AD344">
+        <v>2</v>
+      </c>
       <c r="AE344">
         <v>2008</v>
       </c>
-      <c r="AG344">
-        <v>0</v>
+      <c r="AF344">
+        <v>1</v>
       </c>
       <c r="AH344">
         <v>0</v>
@@ -23349,10 +24672,13 @@
         <v>0</v>
       </c>
       <c r="AK344">
+        <v>0</v>
+      </c>
+      <c r="AL344">
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:37">
+    <row r="345" spans="1:38">
       <c r="A345">
         <v>221999</v>
       </c>
@@ -23371,17 +24697,26 @@
       <c r="F345">
         <v>0</v>
       </c>
-      <c r="G345">
-        <v>0</v>
-      </c>
       <c r="N345">
+        <v>0</v>
+      </c>
+      <c r="T345">
+        <v>0</v>
+      </c>
+      <c r="V345">
+        <v>0</v>
+      </c>
+      <c r="AB345">
+        <v>0</v>
+      </c>
+      <c r="AD345">
         <v>0</v>
       </c>
       <c r="AE345">
         <v>2008</v>
       </c>
-      <c r="AG345">
-        <v>0</v>
+      <c r="AF345">
+        <v>2</v>
       </c>
       <c r="AH345">
         <v>0</v>
@@ -23395,8 +24730,11 @@
       <c r="AK345">
         <v>0</v>
       </c>
-    </row>
-    <row r="346" spans="1:37">
+      <c r="AL345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:38">
       <c r="A346">
         <v>221999</v>
       </c>
@@ -23415,17 +24753,26 @@
       <c r="F346">
         <v>3</v>
       </c>
-      <c r="G346">
-        <v>0</v>
-      </c>
       <c r="N346">
         <v>8</v>
       </c>
+      <c r="T346">
+        <v>0</v>
+      </c>
+      <c r="V346">
+        <v>5</v>
+      </c>
+      <c r="AB346">
+        <v>0</v>
+      </c>
+      <c r="AD346">
+        <v>3</v>
+      </c>
       <c r="AE346">
         <v>2008</v>
       </c>
-      <c r="AG346">
-        <v>0</v>
+      <c r="AF346">
+        <v>1</v>
       </c>
       <c r="AH346">
         <v>0</v>
@@ -23437,10 +24784,13 @@
         <v>0</v>
       </c>
       <c r="AK346">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="347" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL346">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="347" spans="1:38">
       <c r="A347">
         <v>221999</v>
       </c>
@@ -23459,17 +24809,26 @@
       <c r="F347">
         <v>0</v>
       </c>
-      <c r="G347">
-        <v>0</v>
-      </c>
       <c r="N347">
+        <v>0</v>
+      </c>
+      <c r="T347">
+        <v>0</v>
+      </c>
+      <c r="V347">
+        <v>0</v>
+      </c>
+      <c r="AB347">
+        <v>0</v>
+      </c>
+      <c r="AD347">
         <v>0</v>
       </c>
       <c r="AE347">
         <v>2008</v>
       </c>
-      <c r="AG347">
-        <v>0</v>
+      <c r="AF347">
+        <v>2</v>
       </c>
       <c r="AH347">
         <v>0</v>
@@ -23483,8 +24842,11 @@
       <c r="AK347">
         <v>0</v>
       </c>
-    </row>
-    <row r="348" spans="1:37">
+      <c r="AL347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:38">
       <c r="A348">
         <v>221999</v>
       </c>
@@ -23509,11 +24871,23 @@
       <c r="N348">
         <v>0</v>
       </c>
+      <c r="T348">
+        <v>0</v>
+      </c>
+      <c r="V348">
+        <v>0</v>
+      </c>
+      <c r="AB348">
+        <v>0</v>
+      </c>
+      <c r="AD348">
+        <v>0</v>
+      </c>
       <c r="AE348">
         <v>2009</v>
       </c>
-      <c r="AG348">
-        <v>0</v>
+      <c r="AF348">
+        <v>2</v>
       </c>
       <c r="AH348">
         <v>0</v>
@@ -23527,8 +24901,11 @@
       <c r="AK348">
         <v>0</v>
       </c>
-    </row>
-    <row r="349" spans="1:37">
+      <c r="AL348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:38">
       <c r="A349">
         <v>221999</v>
       </c>
@@ -23553,14 +24930,26 @@
       <c r="N349">
         <v>2</v>
       </c>
+      <c r="T349">
+        <v>1</v>
+      </c>
+      <c r="V349">
+        <v>1</v>
+      </c>
+      <c r="AB349">
+        <v>1</v>
+      </c>
+      <c r="AD349">
+        <v>1</v>
+      </c>
       <c r="AE349">
         <v>2009</v>
       </c>
-      <c r="AG349">
+      <c r="AF349">
         <v>1</v>
       </c>
       <c r="AH349">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI349">
         <v>0</v>
@@ -23569,10 +24958,13 @@
         <v>0</v>
       </c>
       <c r="AK349">
+        <v>0</v>
+      </c>
+      <c r="AL349">
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:37">
+    <row r="350" spans="1:38">
       <c r="A350">
         <v>221999</v>
       </c>
@@ -23597,11 +24989,23 @@
       <c r="N350">
         <v>8</v>
       </c>
+      <c r="T350">
+        <v>1</v>
+      </c>
+      <c r="V350">
+        <v>7</v>
+      </c>
+      <c r="AB350">
+        <v>0</v>
+      </c>
+      <c r="AD350">
+        <v>1</v>
+      </c>
       <c r="AE350">
         <v>2009</v>
       </c>
-      <c r="AG350">
-        <v>0</v>
+      <c r="AF350">
+        <v>1</v>
       </c>
       <c r="AH350">
         <v>0</v>
@@ -23610,13 +25014,16 @@
         <v>0</v>
       </c>
       <c r="AJ350">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK350">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="351" spans="1:37">
+        <v>2</v>
+      </c>
+      <c r="AL350">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="351" spans="1:38">
       <c r="A351">
         <v>221999</v>
       </c>
@@ -23641,11 +25048,23 @@
       <c r="N351">
         <v>0</v>
       </c>
+      <c r="T351">
+        <v>0</v>
+      </c>
+      <c r="V351">
+        <v>0</v>
+      </c>
+      <c r="AB351">
+        <v>0</v>
+      </c>
+      <c r="AD351">
+        <v>0</v>
+      </c>
       <c r="AE351">
         <v>2009</v>
       </c>
-      <c r="AG351">
-        <v>0</v>
+      <c r="AF351">
+        <v>2</v>
       </c>
       <c r="AH351">
         <v>0</v>
@@ -23659,8 +25078,11 @@
       <c r="AK351">
         <v>0</v>
       </c>
-    </row>
-    <row r="352" spans="1:37">
+      <c r="AL351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:38">
       <c r="A352">
         <v>221999</v>
       </c>
@@ -23700,8 +25122,8 @@
       <c r="AE352">
         <v>2010</v>
       </c>
-      <c r="AG352">
-        <v>0</v>
+      <c r="AF352">
+        <v>1</v>
       </c>
       <c r="AH352">
         <v>0</v>
@@ -23710,13 +25132,16 @@
         <v>0</v>
       </c>
       <c r="AJ352">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK352">
+        <v>1</v>
+      </c>
+      <c r="AL352">
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:37">
+    <row r="353" spans="1:38">
       <c r="A353">
         <v>221999</v>
       </c>
@@ -23756,8 +25181,8 @@
       <c r="AE353">
         <v>2010</v>
       </c>
-      <c r="AG353">
-        <v>0</v>
+      <c r="AF353">
+        <v>2</v>
       </c>
       <c r="AH353">
         <v>0</v>
@@ -23771,8 +25196,11 @@
       <c r="AK353">
         <v>0</v>
       </c>
-    </row>
-    <row r="354" spans="1:37">
+      <c r="AL353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:38">
       <c r="A354">
         <v>221999</v>
       </c>
@@ -23812,8 +25240,8 @@
       <c r="AE354">
         <v>2010</v>
       </c>
-      <c r="AG354">
-        <v>0</v>
+      <c r="AF354">
+        <v>1</v>
       </c>
       <c r="AH354">
         <v>0</v>
@@ -23825,10 +25253,13 @@
         <v>0</v>
       </c>
       <c r="AK354">
+        <v>0</v>
+      </c>
+      <c r="AL354">
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:37">
+    <row r="355" spans="1:38">
       <c r="A355">
         <v>221999</v>
       </c>
@@ -23868,8 +25299,8 @@
       <c r="AE355">
         <v>2010</v>
       </c>
-      <c r="AG355">
-        <v>0</v>
+      <c r="AF355">
+        <v>2</v>
       </c>
       <c r="AH355">
         <v>0</v>
@@ -23883,8 +25314,11 @@
       <c r="AK355">
         <v>0</v>
       </c>
-    </row>
-    <row r="356" spans="1:37">
+      <c r="AL355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:38">
       <c r="A356">
         <v>221999</v>
       </c>
@@ -23978,8 +25412,11 @@
       <c r="AE356">
         <v>2011</v>
       </c>
-    </row>
-    <row r="357" spans="1:37">
+      <c r="AF356">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:38">
       <c r="A357">
         <v>221999</v>
       </c>
@@ -24073,8 +25510,11 @@
       <c r="AE357">
         <v>2011</v>
       </c>
-    </row>
-    <row r="358" spans="1:37">
+      <c r="AF357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:38">
       <c r="A358">
         <v>221999</v>
       </c>
@@ -24168,8 +25608,11 @@
       <c r="AE358">
         <v>2011</v>
       </c>
-    </row>
-    <row r="359" spans="1:37">
+      <c r="AF358">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359" spans="1:38">
       <c r="A359">
         <v>221999</v>
       </c>
@@ -24263,8 +25706,11 @@
       <c r="AE359">
         <v>2011</v>
       </c>
-    </row>
-    <row r="360" spans="1:37">
+      <c r="AF359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:38">
       <c r="A360">
         <v>227757</v>
       </c>
@@ -24287,10 +25733,10 @@
         <v>2003</v>
       </c>
       <c r="AF360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG360">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH360">
         <v>0</v>
@@ -24304,8 +25750,11 @@
       <c r="AK360">
         <v>0</v>
       </c>
-    </row>
-    <row r="361" spans="1:37">
+      <c r="AL360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:38">
       <c r="A361">
         <v>227757</v>
       </c>
@@ -24328,10 +25777,10 @@
         <v>2003</v>
       </c>
       <c r="AF361">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG361">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH361">
         <v>0</v>
@@ -24343,10 +25792,13 @@
         <v>0</v>
       </c>
       <c r="AK361">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:37">
+        <v>0</v>
+      </c>
+      <c r="AL361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:38">
       <c r="A362">
         <v>236948</v>
       </c>
@@ -24440,8 +25892,11 @@
       <c r="AE362">
         <v>2015</v>
       </c>
-    </row>
-    <row r="363" spans="1:37">
+      <c r="AF362">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:38">
       <c r="A363">
         <v>236948</v>
       </c>
@@ -24535,8 +25990,11 @@
       <c r="AE363">
         <v>2015</v>
       </c>
-    </row>
-    <row r="364" spans="1:37">
+      <c r="AF363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:38">
       <c r="A364">
         <v>236948</v>
       </c>
@@ -24630,8 +26088,11 @@
       <c r="AE364">
         <v>2015</v>
       </c>
-    </row>
-    <row r="365" spans="1:37">
+      <c r="AF364">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:38">
       <c r="A365">
         <v>236948</v>
       </c>
@@ -24725,8 +26186,11 @@
       <c r="AE365">
         <v>2015</v>
       </c>
-    </row>
-    <row r="366" spans="1:37">
+      <c r="AF365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:38">
       <c r="A366">
         <v>236948</v>
       </c>
@@ -24820,8 +26284,11 @@
       <c r="AE366">
         <v>2016</v>
       </c>
-    </row>
-    <row r="367" spans="1:37">
+      <c r="AF366">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:38">
       <c r="A367">
         <v>236948</v>
       </c>
@@ -24915,8 +26382,11 @@
       <c r="AE367">
         <v>2016</v>
       </c>
-    </row>
-    <row r="368" spans="1:37">
+      <c r="AF367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:38">
       <c r="A368">
         <v>236948</v>
       </c>
@@ -25010,8 +26480,11 @@
       <c r="AE368">
         <v>2016</v>
       </c>
-    </row>
-    <row r="369" spans="1:31">
+      <c r="AF368">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:32">
       <c r="A369">
         <v>236948</v>
       </c>
@@ -25105,8 +26578,11 @@
       <c r="AE369">
         <v>2016</v>
       </c>
-    </row>
-    <row r="370" spans="1:31">
+      <c r="AF369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:32">
       <c r="A370">
         <v>236948</v>
       </c>
@@ -25200,8 +26676,11 @@
       <c r="AE370">
         <v>2017</v>
       </c>
-    </row>
-    <row r="371" spans="1:31">
+      <c r="AF370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:32">
       <c r="A371">
         <v>236948</v>
       </c>
@@ -25295,8 +26774,11 @@
       <c r="AE371">
         <v>2017</v>
       </c>
-    </row>
-    <row r="372" spans="1:31">
+      <c r="AF371">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="372" spans="1:32">
       <c r="A372">
         <v>236948</v>
       </c>
@@ -25390,8 +26872,11 @@
       <c r="AE372">
         <v>2017</v>
       </c>
-    </row>
-    <row r="373" spans="1:31">
+      <c r="AF372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:32">
       <c r="A373">
         <v>236948</v>
       </c>
@@ -25484,6 +26969,9 @@
       </c>
       <c r="AE373">
         <v>2017</v>
+      </c>
+      <c r="AF373">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
